--- a/excel/qaromi-nhap-T10.xlsx
+++ b/excel/qaromi-nhap-T10.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3351" uniqueCount="1322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3459" uniqueCount="1359">
   <si>
     <t>id</t>
   </si>
@@ -123,7 +123,7 @@
     <t>Giám đốc</t>
   </si>
   <si>
-    <t>2026-10-06 14:01:39</t>
+    <t>2026-10-06 14:16:45</t>
   </si>
   <si>
     <t>NV002</t>
@@ -3439,6 +3439,117 @@
   </si>
   <si>
     <t>collected_by</t>
+  </si>
+  <si>
+    <t>PT-20260929-001</t>
+  </si>
+  <si>
+    <t>WATER_SALE</t>
+  </si>
+  <si>
+    <t>Thu tiền đơn nhập từ sổ ĐIỀU PHỐI NƯỚC LỌC T10 (dòng 8)</t>
+  </si>
+  <si>
+    <t>PT-20260930-001</t>
+  </si>
+  <si>
+    <t>Thu tiền đơn nhập từ sổ ĐIỀU PHỐI NƯỚC LỌC T10 (dòng 14)</t>
+  </si>
+  <si>
+    <t>PT-20260930-002</t>
+  </si>
+  <si>
+    <t>Thu tiền đơn nhập từ sổ ĐIỀU PHỐI NƯỚC LỌC T10 (dòng 16)</t>
+  </si>
+  <si>
+    <t>PT-20261001-001</t>
+  </si>
+  <si>
+    <t>Thu tiền đơn nhập từ sổ ĐIỀU PHỐI NƯỚC LỌC T10 (dòng 24)</t>
+  </si>
+  <si>
+    <t>PT-20261001-002</t>
+  </si>
+  <si>
+    <t>Thu tiền đơn nhập từ sổ ĐIỀU PHỐI NƯỚC LỌC T10 (dòng 31)</t>
+  </si>
+  <si>
+    <t>PT-20261001-003</t>
+  </si>
+  <si>
+    <t>Thu tiền đơn nhập từ sổ ĐIỀU PHỐI NƯỚC LỌC T10 (dòng 34)</t>
+  </si>
+  <si>
+    <t>PT-20261001-004</t>
+  </si>
+  <si>
+    <t>Thu tiền đơn nhập từ sổ ĐIỀU PHỐI NƯỚC LỌC T10 (dòng 35)</t>
+  </si>
+  <si>
+    <t>PT-20261002-001</t>
+  </si>
+  <si>
+    <t>Thu tiền đơn nhập từ sổ ĐIỀU PHỐI NƯỚC LỌC T10 (dòng 36)</t>
+  </si>
+  <si>
+    <t>PT-20261002-002</t>
+  </si>
+  <si>
+    <t>Thu tiền đơn nhập từ sổ ĐIỀU PHỐI NƯỚC LỌC T10 (dòng 47)</t>
+  </si>
+  <si>
+    <t>PT-20261002-003</t>
+  </si>
+  <si>
+    <t>Thu tiền đơn nhập từ sổ ĐIỀU PHỐI NƯỚC LỌC T10 (dòng 50)</t>
+  </si>
+  <si>
+    <t>PT-20261003-001</t>
+  </si>
+  <si>
+    <t>Thu tiền đơn nhập từ sổ ĐIỀU PHỐI NƯỚC LỌC T10 (dòng 56)</t>
+  </si>
+  <si>
+    <t>PT-20261003-002</t>
+  </si>
+  <si>
+    <t>Thu tiền đơn nhập từ sổ ĐIỀU PHỐI NƯỚC LỌC T10 (dòng 61)</t>
+  </si>
+  <si>
+    <t>PT-20261003-003</t>
+  </si>
+  <si>
+    <t>Thu tiền đơn nhập từ sổ ĐIỀU PHỐI NƯỚC LỌC T10 (dòng 64)</t>
+  </si>
+  <si>
+    <t>PT-20261005-001</t>
+  </si>
+  <si>
+    <t>Thu tiền đơn nhập từ sổ ĐIỀU PHỐI NƯỚC LỌC T10 (dòng 68)</t>
+  </si>
+  <si>
+    <t>PT-20261005-002</t>
+  </si>
+  <si>
+    <t>Thu tiền đơn nhập từ sổ ĐIỀU PHỐI NƯỚC LỌC T10 (dòng 76)</t>
+  </si>
+  <si>
+    <t>PT-20261005-003</t>
+  </si>
+  <si>
+    <t>Thu tiền đơn nhập từ sổ ĐIỀU PHỐI NƯỚC LỌC T10 (dòng 77)</t>
+  </si>
+  <si>
+    <t>PT-20261005-004</t>
+  </si>
+  <si>
+    <t>Thu tiền đơn nhập từ sổ ĐIỀU PHỐI NƯỚC LỌC T10 (dòng 83)</t>
+  </si>
+  <si>
+    <t>PT-20261005-005</t>
+  </si>
+  <si>
+    <t>Thu tiền đơn nhập từ sổ ĐIỀU PHỐI NƯỚC LỌC T10 (dòng 87)</t>
   </si>
   <si>
     <t>expense_code</t>
@@ -13441,7 +13552,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -13477,6 +13588,636 @@
       </c>
       <c r="K1" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>980000</v>
+      </c>
+      <c r="G2" t="s">
+        <v>822</v>
+      </c>
+      <c r="H2">
+        <v>195</v>
+      </c>
+      <c r="I2" t="s">
+        <v>704</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="K2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D3">
+        <v>9</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>490000</v>
+      </c>
+      <c r="G3" t="s">
+        <v>822</v>
+      </c>
+      <c r="H3">
+        <v>195</v>
+      </c>
+      <c r="I3" t="s">
+        <v>834</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1133</v>
+      </c>
+      <c r="K3" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D4">
+        <v>11</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>255000</v>
+      </c>
+      <c r="G4" t="s">
+        <v>812</v>
+      </c>
+      <c r="H4">
+        <v>51</v>
+      </c>
+      <c r="I4" t="s">
+        <v>834</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1135</v>
+      </c>
+      <c r="K4" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D5">
+        <v>19</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>490000</v>
+      </c>
+      <c r="G5" t="s">
+        <v>822</v>
+      </c>
+      <c r="H5">
+        <v>196</v>
+      </c>
+      <c r="I5" t="s">
+        <v>701</v>
+      </c>
+      <c r="J5" t="s">
+        <v>1137</v>
+      </c>
+      <c r="K5" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D6">
+        <v>25</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>260000</v>
+      </c>
+      <c r="G6" t="s">
+        <v>822</v>
+      </c>
+      <c r="H6">
+        <v>195</v>
+      </c>
+      <c r="I6" t="s">
+        <v>701</v>
+      </c>
+      <c r="J6" t="s">
+        <v>1139</v>
+      </c>
+      <c r="K6" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D7">
+        <v>28</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7">
+        <v>52000</v>
+      </c>
+      <c r="G7" t="s">
+        <v>812</v>
+      </c>
+      <c r="H7">
+        <v>38</v>
+      </c>
+      <c r="I7" t="s">
+        <v>701</v>
+      </c>
+      <c r="J7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="K7" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D8">
+        <v>29</v>
+      </c>
+      <c r="E8">
+        <v>17</v>
+      </c>
+      <c r="F8">
+        <v>510000</v>
+      </c>
+      <c r="G8" t="s">
+        <v>822</v>
+      </c>
+      <c r="H8">
+        <v>51</v>
+      </c>
+      <c r="I8" t="s">
+        <v>701</v>
+      </c>
+      <c r="J8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="K8" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D9">
+        <v>30</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>1150000</v>
+      </c>
+      <c r="G9" t="s">
+        <v>822</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9" t="s">
+        <v>921</v>
+      </c>
+      <c r="J9" t="s">
+        <v>1145</v>
+      </c>
+      <c r="K9" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D10">
+        <v>40</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10">
+        <v>980000</v>
+      </c>
+      <c r="G10" t="s">
+        <v>822</v>
+      </c>
+      <c r="H10">
+        <v>4</v>
+      </c>
+      <c r="I10" t="s">
+        <v>921</v>
+      </c>
+      <c r="J10" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K10" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D11">
+        <v>43</v>
+      </c>
+      <c r="E11">
+        <v>20</v>
+      </c>
+      <c r="F11">
+        <v>52000</v>
+      </c>
+      <c r="G11" t="s">
+        <v>822</v>
+      </c>
+      <c r="H11">
+        <v>14</v>
+      </c>
+      <c r="I11" t="s">
+        <v>921</v>
+      </c>
+      <c r="J11" t="s">
+        <v>1149</v>
+      </c>
+      <c r="K11" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D12">
+        <v>49</v>
+      </c>
+      <c r="E12">
+        <v>17</v>
+      </c>
+      <c r="F12">
+        <v>170000</v>
+      </c>
+      <c r="G12" t="s">
+        <v>822</v>
+      </c>
+      <c r="H12">
+        <v>14</v>
+      </c>
+      <c r="I12" t="s">
+        <v>702</v>
+      </c>
+      <c r="J12" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K12" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D13">
+        <v>54</v>
+      </c>
+      <c r="E13">
+        <v>26</v>
+      </c>
+      <c r="F13">
+        <v>144000</v>
+      </c>
+      <c r="G13" t="s">
+        <v>822</v>
+      </c>
+      <c r="H13">
+        <v>4</v>
+      </c>
+      <c r="I13" t="s">
+        <v>702</v>
+      </c>
+      <c r="J13" t="s">
+        <v>1153</v>
+      </c>
+      <c r="K13" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D14">
+        <v>57</v>
+      </c>
+      <c r="E14">
+        <v>28</v>
+      </c>
+      <c r="F14">
+        <v>490000</v>
+      </c>
+      <c r="G14" t="s">
+        <v>822</v>
+      </c>
+      <c r="H14">
+        <v>86</v>
+      </c>
+      <c r="I14" t="s">
+        <v>702</v>
+      </c>
+      <c r="J14" t="s">
+        <v>1155</v>
+      </c>
+      <c r="K14" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D15">
+        <v>61</v>
+      </c>
+      <c r="E15">
+        <v>26</v>
+      </c>
+      <c r="F15">
+        <v>48000</v>
+      </c>
+      <c r="G15" t="s">
+        <v>822</v>
+      </c>
+      <c r="H15">
+        <v>195</v>
+      </c>
+      <c r="I15" t="s">
+        <v>700</v>
+      </c>
+      <c r="J15" t="s">
+        <v>1157</v>
+      </c>
+      <c r="K15" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D16">
+        <v>68</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>980000</v>
+      </c>
+      <c r="G16" t="s">
+        <v>822</v>
+      </c>
+      <c r="H16">
+        <v>195</v>
+      </c>
+      <c r="I16" t="s">
+        <v>700</v>
+      </c>
+      <c r="J16" t="s">
+        <v>1159</v>
+      </c>
+      <c r="K16" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D17">
+        <v>69</v>
+      </c>
+      <c r="E17">
+        <v>26</v>
+      </c>
+      <c r="F17">
+        <v>980000</v>
+      </c>
+      <c r="G17" t="s">
+        <v>822</v>
+      </c>
+      <c r="H17">
+        <v>196</v>
+      </c>
+      <c r="I17" t="s">
+        <v>700</v>
+      </c>
+      <c r="J17" t="s">
+        <v>1161</v>
+      </c>
+      <c r="K17" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D18">
+        <v>74</v>
+      </c>
+      <c r="E18">
+        <v>36</v>
+      </c>
+      <c r="F18">
+        <v>294000</v>
+      </c>
+      <c r="G18" t="s">
+        <v>822</v>
+      </c>
+      <c r="H18">
+        <v>20</v>
+      </c>
+      <c r="I18" t="s">
+        <v>700</v>
+      </c>
+      <c r="J18" t="s">
+        <v>1163</v>
+      </c>
+      <c r="K18" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D19">
+        <v>78</v>
+      </c>
+      <c r="E19">
+        <v>28</v>
+      </c>
+      <c r="F19">
+        <v>294000</v>
+      </c>
+      <c r="G19" t="s">
+        <v>822</v>
+      </c>
+      <c r="H19">
+        <v>86</v>
+      </c>
+      <c r="I19" t="s">
+        <v>700</v>
+      </c>
+      <c r="J19" t="s">
+        <v>1165</v>
+      </c>
+      <c r="K19" t="s">
+        <v>743</v>
       </c>
     </row>
   </sheetData>
@@ -13495,19 +14236,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1129</v>
+        <v>1166</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1130</v>
+        <v>1167</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1127</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1131</v>
+        <v>1168</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1132</v>
+        <v>1169</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
@@ -13516,7 +14257,7 @@
         <v>779</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1133</v>
+        <v>1170</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>713</v>
@@ -13547,13 +14288,13 @@
         <v>477</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1134</v>
+        <v>1171</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1106</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1135</v>
+        <v>1172</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>19</v>
@@ -13587,7 +14328,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1136</v>
+        <v>1173</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>19</v>
@@ -13604,10 +14345,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1137</v>
+        <v>1174</v>
       </c>
       <c r="C2" t="s">
-        <v>1138</v>
+        <v>1175</v>
       </c>
       <c r="D2">
         <v>5000</v>
@@ -13616,7 +14357,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>1139</v>
+        <v>1176</v>
       </c>
     </row>
   </sheetData>
@@ -13647,19 +14388,19 @@
         <v>477</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1140</v>
+        <v>1177</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1141</v>
+        <v>1178</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1142</v>
+        <v>1179</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1143</v>
+        <v>1180</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1144</v>
+        <v>1181</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>19</v>
@@ -17849,13 +18590,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1145</v>
+        <v>1182</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1146</v>
+        <v>1183</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1147</v>
+        <v>1184</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1105</v>
@@ -17864,13 +18605,13 @@
         <v>769</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1148</v>
+        <v>1185</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1149</v>
+        <v>1186</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1150</v>
+        <v>1187</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>526</v>
@@ -17888,7 +18629,7 @@
         <v>781</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>1151</v>
+        <v>1188</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>788</v>
@@ -17900,7 +18641,7 @@
         <v>792</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>1152</v>
+        <v>1189</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>713</v>
@@ -17977,16 +18718,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1153</v>
+        <v>1190</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1154</v>
+        <v>1191</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>662</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1155</v>
+        <v>1192</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>19</v>
@@ -18000,13 +18741,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1156</v>
+        <v>1193</v>
       </c>
       <c r="C2" t="s">
-        <v>1157</v>
+        <v>1194</v>
       </c>
       <c r="E2" t="s">
-        <v>1158</v>
+        <v>1195</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -18015,7 +18756,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>1159</v>
+        <v>1196</v>
       </c>
     </row>
   </sheetData>
@@ -18054,16 +18795,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1160</v>
+        <v>1197</v>
       </c>
       <c r="C2" t="s">
-        <v>1161</v>
+        <v>1198</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>1139</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -18071,16 +18812,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1162</v>
+        <v>1199</v>
       </c>
       <c r="C3" t="s">
-        <v>1163</v>
+        <v>1200</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>1139</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -18088,16 +18829,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1164</v>
+        <v>1201</v>
       </c>
       <c r="C4" t="s">
-        <v>1165</v>
+        <v>1202</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>1139</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -18105,7 +18846,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1166</v>
+        <v>1203</v>
       </c>
       <c r="C5" t="s">
         <v>154</v>
@@ -18114,7 +18855,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>1139</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -18122,7 +18863,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1167</v>
+        <v>1204</v>
       </c>
       <c r="C6" t="s">
         <v>157</v>
@@ -18131,7 +18872,7 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>1139</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -18139,7 +18880,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>1168</v>
+        <v>1205</v>
       </c>
       <c r="C7" t="s">
         <v>355</v>
@@ -18148,7 +18889,7 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>1139</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -18156,7 +18897,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1169</v>
+        <v>1206</v>
       </c>
       <c r="C8" t="s">
         <v>358</v>
@@ -18165,7 +18906,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>1139</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -18173,16 +18914,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1170</v>
+        <v>1207</v>
       </c>
       <c r="C9" t="s">
-        <v>1171</v>
+        <v>1208</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>1139</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -18190,16 +18931,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1172</v>
+        <v>1209</v>
       </c>
       <c r="C10" t="s">
-        <v>1173</v>
+        <v>1210</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>1139</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -18207,16 +18948,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>1174</v>
+        <v>1211</v>
       </c>
       <c r="C11" t="s">
-        <v>1175</v>
+        <v>1212</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>1139</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -18224,16 +18965,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
         <v>1176</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1177</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12" t="s">
-        <v>1139</v>
       </c>
     </row>
   </sheetData>
@@ -18272,10 +19013,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1178</v>
+        <v>1215</v>
       </c>
       <c r="C2" t="s">
-        <v>1179</v>
+        <v>1216</v>
       </c>
       <c r="D2" t="s">
         <v>452</v>
@@ -18284,7 +19025,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>1159</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -18292,10 +19033,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1180</v>
+        <v>1217</v>
       </c>
       <c r="C3" t="s">
-        <v>1181</v>
+        <v>1218</v>
       </c>
       <c r="D3" t="s">
         <v>452</v>
@@ -18304,7 +19045,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>1159</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -18312,10 +19053,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1182</v>
+        <v>1219</v>
       </c>
       <c r="C4" t="s">
-        <v>1183</v>
+        <v>1220</v>
       </c>
       <c r="D4" t="s">
         <v>452</v>
@@ -18324,7 +19065,7 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>1159</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -18332,10 +19073,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1184</v>
+        <v>1221</v>
       </c>
       <c r="C5" t="s">
-        <v>1185</v>
+        <v>1222</v>
       </c>
       <c r="D5" t="s">
         <v>452</v>
@@ -18344,7 +19085,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>1159</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -18352,13 +19093,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1186</v>
+        <v>1223</v>
       </c>
       <c r="C6" t="s">
-        <v>1187</v>
+        <v>1224</v>
       </c>
       <c r="D6" t="s">
-        <v>1188</v>
+        <v>1225</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -18412,28 +19153,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1189</v>
+        <v>1226</v>
       </c>
       <c r="C2" t="s">
-        <v>1190</v>
+        <v>1227</v>
       </c>
       <c r="D2" t="s">
-        <v>1191</v>
+        <v>1228</v>
       </c>
       <c r="E2" t="s">
-        <v>1192</v>
+        <v>1229</v>
       </c>
       <c r="F2" t="s">
-        <v>1193</v>
+        <v>1230</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>1194</v>
+        <v>1231</v>
       </c>
       <c r="I2" t="s">
-        <v>1159</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -18441,28 +19182,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1195</v>
+        <v>1232</v>
       </c>
       <c r="C3" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1235</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1231</v>
+      </c>
+      <c r="I3" t="s">
         <v>1196</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1198</v>
-      </c>
-      <c r="F3" t="s">
-        <v>1199</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3" t="s">
-        <v>1194</v>
-      </c>
-      <c r="I3" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -18470,16 +19211,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1200</v>
+        <v>1237</v>
       </c>
       <c r="C4" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>1202</v>
+        <v>1239</v>
       </c>
       <c r="I4" t="s">
         <v>23</v>
@@ -18490,16 +19231,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1203</v>
+        <v>1240</v>
       </c>
       <c r="C5" t="s">
-        <v>1204</v>
+        <v>1241</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>1202</v>
+        <v>1239</v>
       </c>
       <c r="I5" t="s">
         <v>23</v>
@@ -18510,16 +19251,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1205</v>
+        <v>1242</v>
       </c>
       <c r="C6" t="s">
-        <v>1206</v>
+        <v>1243</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>1202</v>
+        <v>1239</v>
       </c>
       <c r="I6" t="s">
         <v>23</v>
@@ -18530,16 +19271,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>1207</v>
+        <v>1244</v>
       </c>
       <c r="C7" t="s">
-        <v>1208</v>
+        <v>1245</v>
       </c>
       <c r="G7">
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>1202</v>
+        <v>1239</v>
       </c>
       <c r="I7" t="s">
         <v>23</v>
@@ -18550,16 +19291,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1209</v>
+        <v>1246</v>
       </c>
       <c r="C8" t="s">
-        <v>1210</v>
+        <v>1247</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>1202</v>
+        <v>1239</v>
       </c>
       <c r="I8" t="s">
         <v>23</v>
@@ -18581,10 +19322,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1211</v>
+        <v>1248</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1212</v>
+        <v>1249</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1108</v>
@@ -18593,7 +19334,7 @@
         <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1213</v>
+        <v>1250</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>713</v>
@@ -18621,10 +19362,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1214</v>
+        <v>1251</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1215</v>
+        <v>1252</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>694</v>
@@ -18642,28 +19383,28 @@
         <v>1105</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1216</v>
+        <v>1253</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>1113</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1217</v>
+        <v>1254</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1218</v>
+        <v>1255</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>1219</v>
+        <v>1256</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>713</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>1220</v>
+        <v>1257</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>1221</v>
+        <v>1258</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>5</v>
@@ -18691,7 +19432,7 @@
         <v>695</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1222</v>
+        <v>1259</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>696</v>
@@ -18700,7 +19441,7 @@
         <v>709</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1223</v>
+        <v>1260</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>713</v>
@@ -18722,16 +19463,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1224</v>
+        <v>1261</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1225</v>
+        <v>1262</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1226</v>
+        <v>1263</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1227</v>
+        <v>1264</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -18826,13 +19567,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1228</v>
+        <v>1265</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1229</v>
+        <v>1266</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1230</v>
+        <v>1267</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>713</v>
@@ -18846,22 +19587,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1231</v>
+        <v>1268</v>
       </c>
       <c r="C2" t="s">
-        <v>1232</v>
+        <v>1269</v>
       </c>
       <c r="D2">
         <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>1233</v>
+        <v>1270</v>
       </c>
       <c r="G2" t="s">
-        <v>1234</v>
+        <v>1271</v>
       </c>
       <c r="H2" t="s">
-        <v>1139</v>
+        <v>1176</v>
       </c>
     </row>
   </sheetData>
@@ -18883,7 +19624,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1235</v>
+        <v>1272</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>769</v>
@@ -18920,10 +19661,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1236</v>
+        <v>1273</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1237</v>
+        <v>1274</v>
       </c>
     </row>
   </sheetData>
@@ -18942,37 +19683,37 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1238</v>
+        <v>1275</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1239</v>
+        <v>1276</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1240</v>
+        <v>1277</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1241</v>
+        <v>1278</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1242</v>
+        <v>1279</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1243</v>
+        <v>1280</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1244</v>
+        <v>1281</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1245</v>
+        <v>1282</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1246</v>
+        <v>1283</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1247</v>
+        <v>1284</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1248</v>
+        <v>1285</v>
       </c>
     </row>
   </sheetData>
@@ -18994,10 +19735,10 @@
         <v>1105</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1249</v>
+        <v>1286</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1250</v>
+        <v>1287</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>694</v>
@@ -19006,7 +19747,7 @@
         <v>711</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1251</v>
+        <v>1288</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1127</v>
@@ -19034,7 +19775,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1252</v>
+        <v>1289</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>695</v>
@@ -19062,37 +19803,37 @@
         <v>1105</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1253</v>
+        <v>1290</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>711</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1254</v>
+        <v>1291</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1255</v>
+        <v>1292</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1256</v>
+        <v>1293</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1257</v>
+        <v>1294</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1258</v>
+        <v>1295</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1259</v>
+        <v>1296</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1260</v>
+        <v>1297</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1261</v>
+        <v>1298</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1262</v>
+        <v>1299</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>713</v>
@@ -19137,7 +19878,7 @@
         <v>50000</v>
       </c>
       <c r="D2" t="s">
-        <v>1263</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -19151,7 +19892,7 @@
         <v>50000</v>
       </c>
       <c r="D3" t="s">
-        <v>1264</v>
+        <v>1301</v>
       </c>
     </row>
   </sheetData>
@@ -19805,57 +20546,57 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1265</v>
+        <v>1302</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1266</v>
+        <v>1303</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1267</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1268</v>
+        <v>1305</v>
       </c>
       <c r="B2" t="s">
         <v>701</v>
       </c>
       <c r="C2" t="s">
-        <v>1269</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1270</v>
+        <v>1307</v>
       </c>
       <c r="B3" t="s">
-        <v>1271</v>
+        <v>1308</v>
       </c>
       <c r="C3" t="s">
-        <v>1269</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1272</v>
+        <v>1309</v>
       </c>
       <c r="B4" t="s">
-        <v>1273</v>
+        <v>1310</v>
       </c>
       <c r="C4" t="s">
-        <v>1159</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1274</v>
+        <v>1311</v>
       </c>
       <c r="B5" t="s">
-        <v>1273</v>
+        <v>1310</v>
       </c>
       <c r="C5" t="s">
-        <v>1159</v>
+        <v>1196</v>
       </c>
     </row>
   </sheetData>
@@ -19876,18 +20617,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1275</v>
+        <v>1312</v>
       </c>
       <c r="B1" t="s">
-        <v>1276</v>
+        <v>1313</v>
       </c>
       <c r="C1" t="s">
-        <v>1277</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1278</v>
+        <v>1315</v>
       </c>
       <c r="B2" t="s">
         <v>452</v>
@@ -19898,10 +20639,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1279</v>
+        <v>1316</v>
       </c>
       <c r="B3" t="s">
-        <v>1280</v>
+        <v>1317</v>
       </c>
       <c r="C3" t="s">
         <v>452</v>
@@ -19909,10 +20650,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1281</v>
+        <v>1318</v>
       </c>
       <c r="B4" t="s">
-        <v>1282</v>
+        <v>1319</v>
       </c>
       <c r="C4" t="s">
         <v>452</v>
@@ -19920,10 +20661,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1283</v>
+        <v>1320</v>
       </c>
       <c r="B5" t="s">
-        <v>1284</v>
+        <v>1321</v>
       </c>
       <c r="C5" t="s">
         <v>452</v>
@@ -19931,10 +20672,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1285</v>
+        <v>1322</v>
       </c>
       <c r="B6" t="s">
-        <v>1286</v>
+        <v>1323</v>
       </c>
       <c r="C6" t="s">
         <v>452</v>
@@ -19942,10 +20683,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1287</v>
+        <v>1324</v>
       </c>
       <c r="B7" t="s">
-        <v>1288</v>
+        <v>1325</v>
       </c>
       <c r="C7" t="s">
         <v>452</v>
@@ -19953,10 +20694,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1289</v>
+        <v>1326</v>
       </c>
       <c r="B8" t="s">
-        <v>1290</v>
+        <v>1327</v>
       </c>
       <c r="C8" t="s">
         <v>452</v>
@@ -19964,10 +20705,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1291</v>
+        <v>1328</v>
       </c>
       <c r="B9" t="s">
-        <v>1292</v>
+        <v>1329</v>
       </c>
       <c r="C9" t="s">
         <v>452</v>
@@ -19975,10 +20716,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1293</v>
+        <v>1330</v>
       </c>
       <c r="B10" t="s">
-        <v>1294</v>
+        <v>1331</v>
       </c>
       <c r="C10" t="s">
         <v>452</v>
@@ -19986,10 +20727,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1295</v>
+        <v>1332</v>
       </c>
       <c r="B11" t="s">
-        <v>1296</v>
+        <v>1333</v>
       </c>
       <c r="C11" t="s">
         <v>452</v>
@@ -19997,10 +20738,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1297</v>
+        <v>1334</v>
       </c>
       <c r="B12" t="s">
-        <v>1286</v>
+        <v>1323</v>
       </c>
       <c r="C12" t="s">
         <v>452</v>
@@ -20019,7 +20760,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1298</v>
+        <v>1335</v>
       </c>
       <c r="B14" t="s">
         <v>452</v>
@@ -20033,7 +20774,7 @@
         <v>452</v>
       </c>
       <c r="B15" t="s">
-        <v>1299</v>
+        <v>1336</v>
       </c>
       <c r="C15" t="s">
         <v>452</v>
@@ -20044,7 +20785,7 @@
         <v>452</v>
       </c>
       <c r="B16" t="s">
-        <v>1300</v>
+        <v>1337</v>
       </c>
       <c r="C16" t="s">
         <v>452</v>
@@ -20055,7 +20796,7 @@
         <v>452</v>
       </c>
       <c r="B17" t="s">
-        <v>1301</v>
+        <v>1338</v>
       </c>
       <c r="C17" t="s">
         <v>452</v>
@@ -20066,7 +20807,7 @@
         <v>452</v>
       </c>
       <c r="B18" t="s">
-        <v>1302</v>
+        <v>1339</v>
       </c>
       <c r="C18" t="s">
         <v>452</v>
@@ -20077,7 +20818,7 @@
         <v>452</v>
       </c>
       <c r="B19" t="s">
-        <v>1303</v>
+        <v>1340</v>
       </c>
       <c r="C19" t="s">
         <v>452</v>
@@ -20088,7 +20829,7 @@
         <v>452</v>
       </c>
       <c r="B20" t="s">
-        <v>1304</v>
+        <v>1341</v>
       </c>
       <c r="C20" t="s">
         <v>452</v>
@@ -20099,7 +20840,7 @@
         <v>452</v>
       </c>
       <c r="B21" t="s">
-        <v>1305</v>
+        <v>1342</v>
       </c>
       <c r="C21" t="s">
         <v>452</v>
@@ -20110,7 +20851,7 @@
         <v>452</v>
       </c>
       <c r="B22" t="s">
-        <v>1306</v>
+        <v>1343</v>
       </c>
       <c r="C22" t="s">
         <v>452</v>
@@ -20121,7 +20862,7 @@
         <v>452</v>
       </c>
       <c r="B23" t="s">
-        <v>1307</v>
+        <v>1344</v>
       </c>
       <c r="C23" t="s">
         <v>452</v>
@@ -20132,7 +20873,7 @@
         <v>452</v>
       </c>
       <c r="B24" t="s">
-        <v>1308</v>
+        <v>1345</v>
       </c>
       <c r="C24" t="s">
         <v>452</v>
@@ -20143,7 +20884,7 @@
         <v>452</v>
       </c>
       <c r="B25" t="s">
-        <v>1309</v>
+        <v>1346</v>
       </c>
       <c r="C25" t="s">
         <v>452</v>
@@ -20162,7 +20903,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1310</v>
+        <v>1347</v>
       </c>
       <c r="B27" t="s">
         <v>452</v>
@@ -20176,10 +20917,10 @@
         <v>452</v>
       </c>
       <c r="B28" t="s">
-        <v>1311</v>
+        <v>1348</v>
       </c>
       <c r="C28" t="s">
-        <v>1312</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -20195,7 +20936,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1313</v>
+        <v>1350</v>
       </c>
       <c r="B30" t="s">
         <v>452</v>
@@ -20209,7 +20950,7 @@
         <v>452</v>
       </c>
       <c r="B31" t="s">
-        <v>1314</v>
+        <v>1351</v>
       </c>
       <c r="C31" t="s">
         <v>452</v>
@@ -20220,7 +20961,7 @@
         <v>452</v>
       </c>
       <c r="B32" t="s">
-        <v>1315</v>
+        <v>1352</v>
       </c>
       <c r="C32" t="s">
         <v>452</v>
@@ -20231,7 +20972,7 @@
         <v>452</v>
       </c>
       <c r="B33" t="s">
-        <v>1316</v>
+        <v>1353</v>
       </c>
       <c r="C33" t="s">
         <v>452</v>
@@ -20250,7 +20991,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1317</v>
+        <v>1354</v>
       </c>
       <c r="B35" t="s">
         <v>452</v>
@@ -20264,7 +21005,7 @@
         <v>452</v>
       </c>
       <c r="B36" t="s">
-        <v>1318</v>
+        <v>1355</v>
       </c>
       <c r="C36" t="s">
         <v>452</v>
@@ -20275,7 +21016,7 @@
         <v>452</v>
       </c>
       <c r="B37" t="s">
-        <v>1319</v>
+        <v>1356</v>
       </c>
       <c r="C37" t="s">
         <v>452</v>
@@ -20286,7 +21027,7 @@
         <v>452</v>
       </c>
       <c r="B38" t="s">
-        <v>1320</v>
+        <v>1357</v>
       </c>
       <c r="C38" t="s">
         <v>452</v>
@@ -20305,7 +21046,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1321</v>
+        <v>1358</v>
       </c>
       <c r="B40" t="s">
         <v>452</v>

--- a/excel/qaromi-nhap-T10.xlsx
+++ b/excel/qaromi-nhap-T10.xlsx
@@ -123,7 +123,7 @@
     <t>Giám đốc</t>
   </si>
   <si>
-    <t>2026-10-06 14:16:45</t>
+    <t>2026-10-07 00:51:51</t>
   </si>
   <si>
     <t>NV002</t>
@@ -1515,7 +1515,7 @@
     <t>RO_19L_VOI</t>
   </si>
   <si>
-    <t>Nước Tinh Khiết RO QAROMI 19L (Bình Vòi)</t>
+    <t>Bình RO-Vòi</t>
   </si>
   <si>
     <t>Bình</t>
@@ -1533,7 +1533,7 @@
     <t>RO_19L_UP</t>
   </si>
   <si>
-    <t>Nước Tinh Khiết RO QAROMI 19L (Bình Úp)</t>
+    <t>Bình RO-Úp</t>
   </si>
   <si>
     <t>UP</t>
@@ -1542,19 +1542,19 @@
     <t>KIEM_19L_VOI</t>
   </si>
   <si>
-    <t>Nước Ion Kiềm QAROMI 19L (Bình Vòi)</t>
+    <t>Bình Kiềm-Vòi</t>
   </si>
   <si>
     <t>KIEM_19L_UP</t>
   </si>
   <si>
-    <t>Nước Ion Kiềm QAROMI 19L (Bình Úp)</t>
+    <t>Bình Kiềm-Úp</t>
   </si>
   <si>
     <t>VI_350ML</t>
   </si>
   <si>
-    <t>Nước Chai QAROMI 350ml (Vỉ)</t>
+    <t>Vỉ 350ml</t>
   </si>
   <si>
     <t>Vỉ</t>
@@ -1566,7 +1566,7 @@
     <t>HOP_350ML</t>
   </si>
   <si>
-    <t>Nước Chai QAROMI 350ml (Hộp)</t>
+    <t>Hộp 350ml</t>
   </si>
   <si>
     <t>Hộp</t>
@@ -1575,13 +1575,13 @@
     <t>VI_500ML</t>
   </si>
   <si>
-    <t>Nước Chai QAROMI 500ml (Vỉ)</t>
+    <t>Vỉ 500ml</t>
   </si>
   <si>
     <t>HOP_500ML</t>
   </si>
   <si>
-    <t>Nước Chai QAROMI 500ml (Hộp)</t>
+    <t>Hộp 500ml</t>
   </si>
   <si>
     <t>DV_BINH_NL</t>
@@ -4062,37 +4062,37 @@
     <t>TỒN ĐẦU KỲ 28/9/2026</t>
   </si>
   <si>
-    <t>KHO_HUE / Nước Ion Kiềm QAROMI 19L (Bình Vòi): 8</t>
-  </si>
-  <si>
-    <t>KHO_HUE / Nước Chai QAROMI 500ml (Vỉ): 192</t>
-  </si>
-  <si>
-    <t>KHO_HUE / Nước Chai QAROMI 350ml (Vỉ): 11</t>
-  </si>
-  <si>
-    <t>KHO_TANGAP / Nước Tinh Khiết RO QAROMI 19L (Bình Vòi): 1</t>
-  </si>
-  <si>
-    <t>KHO_TANGAP / Nước Ion Kiềm QAROMI 19L (Bình Vòi): 7</t>
-  </si>
-  <si>
-    <t>KHO_TANGAP / Nước Chai QAROMI 500ml (Vỉ): 214</t>
-  </si>
-  <si>
-    <t>KHO_TANGAP / Nước Chai QAROMI 350ml (Vỉ): 4</t>
-  </si>
-  <si>
-    <t>KHO_VP / Nước Ion Kiềm QAROMI 19L (Bình Vòi): 1</t>
-  </si>
-  <si>
-    <t>KHO_VP / Nước Chai QAROMI 500ml (Vỉ): 24</t>
-  </si>
-  <si>
-    <t>KHO_HALAM / Nước Chai QAROMI 500ml (Vỉ): 17</t>
-  </si>
-  <si>
-    <t>KHO_HALAM / Nước Chai QAROMI 350ml (Vỉ): 30</t>
+    <t>KHO_HUE / Bình Kiềm-Vòi: 8</t>
+  </si>
+  <si>
+    <t>KHO_HUE / Vỉ 500ml: 192</t>
+  </si>
+  <si>
+    <t>KHO_HUE / Vỉ 350ml: 11</t>
+  </si>
+  <si>
+    <t>KHO_TANGAP / Bình RO-Vòi: 1</t>
+  </si>
+  <si>
+    <t>KHO_TANGAP / Bình Kiềm-Vòi: 7</t>
+  </si>
+  <si>
+    <t>KHO_TANGAP / Vỉ 500ml: 214</t>
+  </si>
+  <si>
+    <t>KHO_TANGAP / Vỉ 350ml: 4</t>
+  </si>
+  <si>
+    <t>KHO_VP / Bình Kiềm-Vòi: 1</t>
+  </si>
+  <si>
+    <t>KHO_VP / Vỉ 500ml: 24</t>
+  </si>
+  <si>
+    <t>KHO_HALAM / Vỉ 500ml: 17</t>
+  </si>
+  <si>
+    <t>KHO_HALAM / Vỉ 350ml: 30</t>
   </si>
   <si>
     <t>KHO KHÔNG NHẬN RA (đã tạm xếp vào kho Tăng Áp)</t>

--- a/excel/qaromi-nhap-T10.xlsx
+++ b/excel/qaromi-nhap-T10.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3459" uniqueCount="1359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3443" uniqueCount="1353">
   <si>
     <t>id</t>
   </si>
@@ -123,7 +123,7 @@
     <t>Giám đốc</t>
   </si>
   <si>
-    <t>2026-10-07 00:51:51</t>
+    <t>2026-10-07 15:42:35</t>
   </si>
   <si>
     <t>NV002</t>
@@ -2163,7 +2163,7 @@
     <t>2026-10-03</t>
   </si>
   <si>
-    <t>2026-10-09</t>
+    <t>2026-09-28</t>
   </si>
   <si>
     <t>2026-09-29</t>
@@ -2325,18 +2325,6 @@
     <t>Nhập kho theo sổ T10 ngày 2026-10-01 — tồn xe (hàng Cẩm Phả chở về kho)</t>
   </si>
   <si>
-    <t>T10-2026-10-09</t>
-  </si>
-  <si>
-    <t>Nhập kho theo sổ T10 ngày 2026-10-09 — Tồn kho VP (hàng Cẩm Phả chở về kho)</t>
-  </si>
-  <si>
-    <t>2026-10-09 00:00:00</t>
-  </si>
-  <si>
-    <t>Xuất kho theo sổ T10 ngày 2026-10-09 — Tồn kho VP</t>
-  </si>
-  <si>
     <t>Xuất kho theo sổ T10 ngày 2026-10-02 — Tồn kho VP</t>
   </si>
   <si>
@@ -2347,12 +2335,6 @@
   </si>
   <si>
     <t>Xuất kho theo sổ T10 ngày 2026-10-05 — Tồn kho VP</t>
-  </si>
-  <si>
-    <t>Nhập kho theo sổ T10 ngày 2026-10-09 — TỒN KHO HÀ LẦM (hàng Cẩm Phả chở về kho)</t>
-  </si>
-  <si>
-    <t>Xuất kho theo sổ T10 ngày 2026-10-09 — TỒN KHO HÀ LẦM</t>
   </si>
   <si>
     <t>Xuất kho theo sổ T10 ngày 2026-09-29 — TỒN KHO HÀ LẦM</t>
@@ -4548,124 +4530,124 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>768</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>769</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>772</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>774</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>694</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>800</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>802</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>804</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>805</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>806</v>
       </c>
       <c r="AP1" s="1" t="s">
         <v>713</v>
@@ -4679,7 +4661,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -4688,10 +4670,10 @@
         <v>194</v>
       </c>
       <c r="E2" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G2" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H2">
         <v>195</v>
@@ -4706,13 +4688,13 @@
         <v>704</v>
       </c>
       <c r="L2" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M2" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N2" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -4748,10 +4730,10 @@
         <v>452</v>
       </c>
       <c r="AF2" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="AP2" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="AQ2" t="s">
         <v>23</v>
@@ -4762,19 +4744,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H3">
         <v>195</v>
@@ -4789,13 +4771,13 @@
         <v>704</v>
       </c>
       <c r="L3" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M3" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N3" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -4831,10 +4813,10 @@
         <v>452</v>
       </c>
       <c r="AF3" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="AP3" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="AQ3" t="s">
         <v>23</v>
@@ -4845,7 +4827,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -4854,10 +4836,10 @@
         <v>195</v>
       </c>
       <c r="E4" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G4" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H4">
         <v>195</v>
@@ -4872,13 +4854,13 @@
         <v>704</v>
       </c>
       <c r="L4" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M4" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="N4" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -4914,10 +4896,10 @@
         <v>543</v>
       </c>
       <c r="AF4" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="AP4" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="AQ4" t="s">
         <v>23</v>
@@ -4928,7 +4910,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -4937,10 +4919,10 @@
         <v>195</v>
       </c>
       <c r="E5" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G5" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H5">
         <v>195</v>
@@ -4955,13 +4937,13 @@
         <v>704</v>
       </c>
       <c r="L5" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M5" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N5" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -4997,10 +4979,10 @@
         <v>547</v>
       </c>
       <c r="AF5" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="AP5" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="AQ5" t="s">
         <v>23</v>
@@ -5011,7 +4993,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -5020,10 +5002,10 @@
         <v>195</v>
       </c>
       <c r="E6" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G6" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H6">
         <v>195</v>
@@ -5038,13 +5020,13 @@
         <v>704</v>
       </c>
       <c r="L6" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M6" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N6" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -5074,16 +5056,16 @@
         <v>539</v>
       </c>
       <c r="AD6" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="AE6" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="AF6" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="AP6" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="AQ6" t="s">
         <v>23</v>
@@ -5094,7 +5076,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -5103,10 +5085,10 @@
         <v>195</v>
       </c>
       <c r="E7" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G7" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H7">
         <v>195</v>
@@ -5115,19 +5097,19 @@
         <v>2</v>
       </c>
       <c r="J7" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="K7" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="L7" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M7" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N7" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -5163,10 +5145,10 @@
         <v>551</v>
       </c>
       <c r="AF7" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="AP7" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="AQ7" t="s">
         <v>23</v>
@@ -5177,7 +5159,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="C8">
         <v>6</v>
@@ -5186,10 +5168,10 @@
         <v>195</v>
       </c>
       <c r="E8" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G8" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H8">
         <v>195</v>
@@ -5198,19 +5180,19 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="K8" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="L8" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M8" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N8" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -5246,10 +5228,10 @@
         <v>554</v>
       </c>
       <c r="AF8" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="AP8" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="AQ8" t="s">
         <v>23</v>
@@ -5260,7 +5242,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -5269,10 +5251,10 @@
         <v>195</v>
       </c>
       <c r="E9" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G9" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H9">
         <v>195</v>
@@ -5281,19 +5263,19 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="K9" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="L9" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M9" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N9" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -5323,16 +5305,16 @@
         <v>539</v>
       </c>
       <c r="AD9" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="AE9" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="AF9" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="AP9" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="AQ9" t="s">
         <v>23</v>
@@ -5343,7 +5325,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="C10">
         <v>7</v>
@@ -5352,10 +5334,10 @@
         <v>195</v>
       </c>
       <c r="E10" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G10" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H10">
         <v>195</v>
@@ -5364,19 +5346,19 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="K10" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="L10" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M10" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="N10" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -5412,10 +5394,10 @@
         <v>558</v>
       </c>
       <c r="AF10" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="AP10" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="AQ10" t="s">
         <v>23</v>
@@ -5426,7 +5408,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="C11">
         <v>8</v>
@@ -5435,10 +5417,10 @@
         <v>195</v>
       </c>
       <c r="E11" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G11" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H11">
         <v>195</v>
@@ -5447,19 +5429,19 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="K11" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="L11" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M11" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N11" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -5498,7 +5480,7 @@
         <v>561</v>
       </c>
       <c r="AP11" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
       <c r="AQ11" t="s">
         <v>23</v>
@@ -5509,7 +5491,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -5518,10 +5500,10 @@
         <v>195</v>
       </c>
       <c r="E12" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G12" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H12">
         <v>51</v>
@@ -5530,19 +5512,19 @@
         <v>2</v>
       </c>
       <c r="J12" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="K12" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="L12" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M12" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="N12" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -5575,13 +5557,13 @@
         <v>550</v>
       </c>
       <c r="AE12" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="AF12" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="AP12" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="AQ12" t="s">
         <v>23</v>
@@ -5592,19 +5574,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="F13">
         <v>4</v>
       </c>
       <c r="G13" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H13">
         <v>195</v>
@@ -5613,19 +5595,19 @@
         <v>2</v>
       </c>
       <c r="J13" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="K13" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="L13" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M13" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N13" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -5655,16 +5637,16 @@
         <v>539</v>
       </c>
       <c r="AD13" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="AE13" t="s">
         <v>452</v>
       </c>
       <c r="AF13" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="AP13" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="AQ13" t="s">
         <v>23</v>
@@ -5675,7 +5657,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="C14">
         <v>9</v>
@@ -5684,10 +5666,10 @@
         <v>134</v>
       </c>
       <c r="E14" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G14" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H14">
         <v>134</v>
@@ -5696,19 +5678,19 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="K14" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="L14" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M14" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N14" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -5747,7 +5729,7 @@
         <v>563</v>
       </c>
       <c r="AP14" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="AQ14" t="s">
         <v>23</v>
@@ -5758,7 +5740,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="C15">
         <v>10</v>
@@ -5767,10 +5749,10 @@
         <v>51</v>
       </c>
       <c r="E15" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G15" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H15">
         <v>51</v>
@@ -5779,19 +5761,19 @@
         <v>2</v>
       </c>
       <c r="J15" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="K15" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="L15" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M15" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N15" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -5827,10 +5809,10 @@
         <v>452</v>
       </c>
       <c r="AF15" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="AP15" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="AQ15" t="s">
         <v>23</v>
@@ -5841,7 +5823,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="C16">
         <v>11</v>
@@ -5850,10 +5832,10 @@
         <v>176</v>
       </c>
       <c r="E16" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G16" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H16">
         <v>176</v>
@@ -5862,19 +5844,19 @@
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="K16" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="L16" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M16" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N16" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -5910,10 +5892,10 @@
         <v>452</v>
       </c>
       <c r="AF16" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="AP16" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="AQ16" t="s">
         <v>23</v>
@@ -5924,7 +5906,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="C17">
         <v>4</v>
@@ -5933,10 +5915,10 @@
         <v>195</v>
       </c>
       <c r="E17" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G17" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H17">
         <v>195</v>
@@ -5951,13 +5933,13 @@
         <v>701</v>
       </c>
       <c r="L17" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M17" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N17" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -5984,19 +5966,19 @@
         <v>0</v>
       </c>
       <c r="AC17" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="AD17" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="AE17" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="AF17" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="AP17" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="AQ17" t="s">
         <v>23</v>
@@ -6007,7 +5989,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -6016,10 +5998,10 @@
         <v>51</v>
       </c>
       <c r="E18" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G18" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H18">
         <v>51</v>
@@ -6034,13 +6016,13 @@
         <v>701</v>
       </c>
       <c r="L18" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M18" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N18" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -6076,10 +6058,10 @@
         <v>452</v>
       </c>
       <c r="AF18" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="AP18" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="AQ18" t="s">
         <v>23</v>
@@ -6090,7 +6072,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -6099,10 +6081,10 @@
         <v>195</v>
       </c>
       <c r="E19" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G19" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H19">
         <v>195</v>
@@ -6117,13 +6099,13 @@
         <v>701</v>
       </c>
       <c r="L19" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M19" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N19" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -6156,13 +6138,13 @@
         <v>452</v>
       </c>
       <c r="AE19" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="AF19" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="AP19" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="AQ19" t="s">
         <v>23</v>
@@ -6173,7 +6155,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -6182,13 +6164,13 @@
         <v>195</v>
       </c>
       <c r="E20" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
       <c r="F20">
         <v>2</v>
       </c>
       <c r="G20" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H20">
         <v>196</v>
@@ -6203,13 +6185,13 @@
         <v>701</v>
       </c>
       <c r="L20" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M20" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="N20" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -6239,16 +6221,16 @@
         <v>539</v>
       </c>
       <c r="AD20" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
       <c r="AE20" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
       <c r="AF20" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
       <c r="AP20" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="AQ20" t="s">
         <v>23</v>
@@ -6259,7 +6241,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -6268,10 +6250,10 @@
         <v>195</v>
       </c>
       <c r="E21" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G21" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H21">
         <v>195</v>
@@ -6286,13 +6268,13 @@
         <v>701</v>
       </c>
       <c r="L21" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M21" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N21" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -6322,16 +6304,16 @@
         <v>539</v>
       </c>
       <c r="AD21" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="AE21" t="s">
         <v>452</v>
       </c>
       <c r="AF21" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="AP21" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
       <c r="AQ21" t="s">
         <v>23</v>
@@ -6342,7 +6324,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -6351,10 +6333,10 @@
         <v>195</v>
       </c>
       <c r="E22" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G22" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H22">
         <v>195</v>
@@ -6369,13 +6351,13 @@
         <v>701</v>
       </c>
       <c r="L22" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M22" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N22" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -6405,16 +6387,16 @@
         <v>539</v>
       </c>
       <c r="AD22" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="AE22" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
       <c r="AF22" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="AP22" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="AQ22" t="s">
         <v>23</v>
@@ -6425,7 +6407,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="C23">
         <v>2</v>
@@ -6434,10 +6416,10 @@
         <v>195</v>
       </c>
       <c r="E23" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G23" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H23">
         <v>82</v>
@@ -6452,13 +6434,13 @@
         <v>701</v>
       </c>
       <c r="L23" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M23" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N23" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -6488,16 +6470,16 @@
         <v>539</v>
       </c>
       <c r="AD23" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="AE23" t="s">
         <v>452</v>
       </c>
       <c r="AF23" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="AP23" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="AQ23" t="s">
         <v>23</v>
@@ -6508,7 +6490,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="C24">
         <v>12</v>
@@ -6517,10 +6499,10 @@
         <v>195</v>
       </c>
       <c r="E24" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G24" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H24">
         <v>195</v>
@@ -6535,13 +6517,13 @@
         <v>701</v>
       </c>
       <c r="L24" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M24" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N24" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -6577,10 +6559,10 @@
         <v>571</v>
       </c>
       <c r="AF24" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="AP24" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="AQ24" t="s">
         <v>23</v>
@@ -6591,7 +6573,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
       <c r="C25">
         <v>13</v>
@@ -6600,10 +6582,10 @@
         <v>51</v>
       </c>
       <c r="E25" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G25" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H25">
         <v>195</v>
@@ -6618,13 +6600,13 @@
         <v>701</v>
       </c>
       <c r="L25" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M25" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N25" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -6660,10 +6642,10 @@
         <v>452</v>
       </c>
       <c r="AF25" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="AP25" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="AQ25" t="s">
         <v>23</v>
@@ -6674,7 +6656,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="C26">
         <v>14</v>
@@ -6683,10 +6665,10 @@
         <v>195</v>
       </c>
       <c r="E26" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G26" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H26">
         <v>195</v>
@@ -6701,13 +6683,13 @@
         <v>701</v>
       </c>
       <c r="L26" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M26" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="N26" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -6743,10 +6725,10 @@
         <v>452</v>
       </c>
       <c r="AF26" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="AP26" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
       <c r="AQ26" t="s">
         <v>23</v>
@@ -6757,7 +6739,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="C27">
         <v>15</v>
@@ -6766,10 +6748,10 @@
         <v>14</v>
       </c>
       <c r="E27" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G27" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H27">
         <v>195</v>
@@ -6784,13 +6766,13 @@
         <v>701</v>
       </c>
       <c r="L27" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M27" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N27" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -6826,10 +6808,10 @@
         <v>580</v>
       </c>
       <c r="AF27" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="AP27" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="AQ27" t="s">
         <v>23</v>
@@ -6840,7 +6822,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>910</v>
+        <v>904</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -6849,13 +6831,13 @@
         <v>199</v>
       </c>
       <c r="E28" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
       <c r="F28">
         <v>2</v>
       </c>
       <c r="G28" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H28">
         <v>196</v>
@@ -6870,13 +6852,13 @@
         <v>701</v>
       </c>
       <c r="L28" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M28" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N28" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -6906,16 +6888,16 @@
         <v>539</v>
       </c>
       <c r="AD28" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
       <c r="AE28" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
       <c r="AF28" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
       <c r="AP28" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
       <c r="AQ28" t="s">
         <v>23</v>
@@ -6926,7 +6908,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="C29">
         <v>16</v>
@@ -6935,10 +6917,10 @@
         <v>200</v>
       </c>
       <c r="E29" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G29" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H29">
         <v>38</v>
@@ -6953,13 +6935,13 @@
         <v>701</v>
       </c>
       <c r="L29" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M29" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="N29" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -6995,10 +6977,10 @@
         <v>584</v>
       </c>
       <c r="AF29" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="AP29" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="AQ29" t="s">
         <v>23</v>
@@ -7009,7 +6991,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C30">
         <v>17</v>
@@ -7018,10 +7000,10 @@
         <v>51</v>
       </c>
       <c r="E30" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G30" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H30">
         <v>51</v>
@@ -7036,13 +7018,13 @@
         <v>701</v>
       </c>
       <c r="L30" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M30" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="N30" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -7078,10 +7060,10 @@
         <v>588</v>
       </c>
       <c r="AF30" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="AP30" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="AQ30" t="s">
         <v>23</v>
@@ -7092,7 +7074,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -7101,10 +7083,10 @@
         <v>195</v>
       </c>
       <c r="E31" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G31" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H31">
         <v>4</v>
@@ -7113,19 +7095,19 @@
         <v>2</v>
       </c>
       <c r="J31" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="K31" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="L31" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M31" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="N31" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -7155,16 +7137,16 @@
         <v>539</v>
       </c>
       <c r="AD31" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
       <c r="AE31" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="AF31" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
       <c r="AP31" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="AQ31" t="s">
         <v>23</v>
@@ -7175,19 +7157,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
       <c r="E32" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="F32">
         <v>2</v>
       </c>
       <c r="G32" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H32">
         <v>4</v>
@@ -7196,19 +7178,19 @@
         <v>2</v>
       </c>
       <c r="J32" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="K32" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="L32" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M32" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N32" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -7241,13 +7223,13 @@
         <v>452</v>
       </c>
       <c r="AE32" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="AF32" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="AP32" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="AQ32" t="s">
         <v>23</v>
@@ -7258,7 +7240,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="C33">
         <v>18</v>
@@ -7267,10 +7249,10 @@
         <v>195</v>
       </c>
       <c r="E33" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G33" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H33">
         <v>4</v>
@@ -7279,19 +7261,19 @@
         <v>2</v>
       </c>
       <c r="J33" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="K33" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="L33" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M33" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N33" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -7327,10 +7309,10 @@
         <v>452</v>
       </c>
       <c r="AF33" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="AP33" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="AQ33" t="s">
         <v>23</v>
@@ -7341,7 +7323,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -7350,13 +7332,13 @@
         <v>196</v>
       </c>
       <c r="E34" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
       <c r="F34">
         <v>2</v>
       </c>
       <c r="G34" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H34">
         <v>4</v>
@@ -7365,19 +7347,19 @@
         <v>7</v>
       </c>
       <c r="J34" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="K34" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="L34" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M34" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N34" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -7407,16 +7389,16 @@
         <v>539</v>
       </c>
       <c r="AD34" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
       <c r="AE34" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="AF34" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="AP34" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="AQ34" t="s">
         <v>23</v>
@@ -7427,19 +7409,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="C35">
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H35">
         <v>4</v>
@@ -7448,19 +7430,19 @@
         <v>2</v>
       </c>
       <c r="J35" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="K35" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="L35" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M35" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N35" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -7493,13 +7475,13 @@
         <v>550</v>
       </c>
       <c r="AE35" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="AF35" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="AP35" t="s">
-        <v>940</v>
+        <v>934</v>
       </c>
       <c r="AQ35" t="s">
         <v>23</v>
@@ -7510,7 +7492,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -7519,10 +7501,10 @@
         <v>195</v>
       </c>
       <c r="E36" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G36" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H36">
         <v>4</v>
@@ -7531,19 +7513,19 @@
         <v>2</v>
       </c>
       <c r="J36" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="K36" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="L36" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M36" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N36" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -7579,10 +7561,10 @@
         <v>452</v>
       </c>
       <c r="AF36" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
       <c r="AP36" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="AQ36" t="s">
         <v>23</v>
@@ -7593,7 +7575,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -7602,10 +7584,10 @@
         <v>195</v>
       </c>
       <c r="E37" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G37" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H37">
         <v>4</v>
@@ -7614,19 +7596,19 @@
         <v>4</v>
       </c>
       <c r="J37" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="K37" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="L37" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M37" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N37" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -7659,13 +7641,13 @@
         <v>452</v>
       </c>
       <c r="AE37" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="AF37" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="AP37" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="AQ37" t="s">
         <v>23</v>
@@ -7676,37 +7658,37 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="C38">
         <v>2</v>
       </c>
       <c r="E38" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="F38">
         <v>2</v>
       </c>
       <c r="G38" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="I38">
         <v>3</v>
       </c>
       <c r="J38" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="K38" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="L38" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M38" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N38" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -7736,16 +7718,16 @@
         <v>539</v>
       </c>
       <c r="AD38" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="AE38" t="s">
         <v>452</v>
       </c>
       <c r="AF38" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="AP38" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="AQ38" t="s">
         <v>23</v>
@@ -7756,19 +7738,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="C39">
         <v>2</v>
       </c>
       <c r="E39" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="F39">
         <v>2</v>
       </c>
       <c r="G39" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H39">
         <v>4</v>
@@ -7777,19 +7759,19 @@
         <v>2</v>
       </c>
       <c r="J39" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="K39" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="L39" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M39" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N39" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -7822,13 +7804,13 @@
         <v>452</v>
       </c>
       <c r="AE39" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="AF39" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="AP39" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="AQ39" t="s">
         <v>23</v>
@@ -7839,7 +7821,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="C40">
         <v>19</v>
@@ -7848,10 +7830,10 @@
         <v>195</v>
       </c>
       <c r="E40" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G40" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H40">
         <v>4</v>
@@ -7860,19 +7842,19 @@
         <v>2</v>
       </c>
       <c r="J40" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="K40" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="L40" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M40" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N40" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -7908,10 +7890,10 @@
         <v>595</v>
       </c>
       <c r="AF40" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="AP40" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="AQ40" t="s">
         <v>23</v>
@@ -7922,7 +7904,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -7931,10 +7913,10 @@
         <v>195</v>
       </c>
       <c r="E41" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G41" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H41">
         <v>4</v>
@@ -7943,19 +7925,19 @@
         <v>2</v>
       </c>
       <c r="J41" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="K41" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="L41" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M41" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="N41" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -7985,16 +7967,16 @@
         <v>539</v>
       </c>
       <c r="AD41" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="AE41" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="AF41" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="AP41" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="AQ41" t="s">
         <v>23</v>
@@ -8005,7 +7987,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -8014,10 +7996,10 @@
         <v>195</v>
       </c>
       <c r="E42" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G42" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H42">
         <v>4</v>
@@ -8026,19 +8008,19 @@
         <v>2</v>
       </c>
       <c r="J42" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="K42" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="L42" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M42" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N42" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -8071,13 +8053,13 @@
         <v>452</v>
       </c>
       <c r="AE42" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="AF42" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="AP42" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="AQ42" t="s">
         <v>23</v>
@@ -8088,19 +8070,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="C43">
         <v>2</v>
       </c>
       <c r="E43" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="F43">
         <v>2</v>
       </c>
       <c r="G43" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H43">
         <v>14</v>
@@ -8109,19 +8091,19 @@
         <v>1</v>
       </c>
       <c r="J43" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="K43" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="L43" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M43" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N43" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -8154,13 +8136,13 @@
         <v>452</v>
       </c>
       <c r="AE43" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="AF43" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="AP43" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="AQ43" t="s">
         <v>23</v>
@@ -8171,7 +8153,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="C44">
         <v>20</v>
@@ -8180,10 +8162,10 @@
         <v>14</v>
       </c>
       <c r="E44" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G44" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H44">
         <v>14</v>
@@ -8192,19 +8174,19 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="K44" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="L44" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M44" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="N44" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -8240,10 +8222,10 @@
         <v>452</v>
       </c>
       <c r="AF44" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="AP44" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="AQ44" t="s">
         <v>23</v>
@@ -8254,7 +8236,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="C45">
         <v>21</v>
@@ -8263,10 +8245,10 @@
         <v>10</v>
       </c>
       <c r="E45" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G45" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H45">
         <v>10</v>
@@ -8275,19 +8257,19 @@
         <v>3</v>
       </c>
       <c r="J45" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="K45" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="L45" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M45" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N45" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O45">
         <v>0</v>
@@ -8323,10 +8305,10 @@
         <v>452</v>
       </c>
       <c r="AF45" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="AP45" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="AQ45" t="s">
         <v>23</v>
@@ -8337,7 +8319,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="C46">
         <v>2</v>
@@ -8346,10 +8328,10 @@
         <v>195</v>
       </c>
       <c r="E46" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G46" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H46">
         <v>4</v>
@@ -8358,19 +8340,19 @@
         <v>2</v>
       </c>
       <c r="J46" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="K46" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="L46" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M46" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N46" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -8403,13 +8385,13 @@
         <v>452</v>
       </c>
       <c r="AE46" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="AF46" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="AP46" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="AQ46" t="s">
         <v>23</v>
@@ -8420,7 +8402,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
       <c r="C47">
         <v>22</v>
@@ -8429,10 +8411,10 @@
         <v>51</v>
       </c>
       <c r="E47" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G47" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H47">
         <v>4</v>
@@ -8441,19 +8423,19 @@
         <v>2</v>
       </c>
       <c r="J47" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="K47" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="L47" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M47" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N47" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O47">
         <v>0</v>
@@ -8489,10 +8471,10 @@
         <v>452</v>
       </c>
       <c r="AF47" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="AP47" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="AQ47" t="s">
         <v>23</v>
@@ -8503,19 +8485,19 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="C48">
         <v>23</v>
       </c>
       <c r="E48" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="F48">
         <v>5</v>
       </c>
       <c r="G48" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="I48">
         <v>3</v>
@@ -8527,13 +8509,13 @@
         <v>702</v>
       </c>
       <c r="L48" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M48" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N48" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -8569,10 +8551,10 @@
         <v>452</v>
       </c>
       <c r="AF48" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="AP48" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="AQ48" t="s">
         <v>23</v>
@@ -8583,19 +8565,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="C49">
         <v>2</v>
       </c>
       <c r="E49" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="F49">
         <v>2</v>
       </c>
       <c r="G49" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="I49">
         <v>1</v>
@@ -8607,13 +8589,13 @@
         <v>702</v>
       </c>
       <c r="L49" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M49" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N49" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O49">
         <v>0</v>
@@ -8646,13 +8628,13 @@
         <v>452</v>
       </c>
       <c r="AE49" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="AF49" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="AP49" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="AQ49" t="s">
         <v>23</v>
@@ -8663,7 +8645,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="C50">
         <v>17</v>
@@ -8672,10 +8654,10 @@
         <v>14</v>
       </c>
       <c r="E50" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G50" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H50">
         <v>14</v>
@@ -8690,13 +8672,13 @@
         <v>702</v>
       </c>
       <c r="L50" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M50" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="N50" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="O50">
         <v>0</v>
@@ -8723,19 +8705,19 @@
         <v>170000</v>
       </c>
       <c r="AC50" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="AD50" t="s">
         <v>587</v>
       </c>
       <c r="AE50" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="AF50" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="AP50" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="AQ50" t="s">
         <v>23</v>
@@ -8746,7 +8728,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -8755,10 +8737,10 @@
         <v>195</v>
       </c>
       <c r="E51" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G51" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="I51">
         <v>2</v>
@@ -8770,13 +8752,13 @@
         <v>702</v>
       </c>
       <c r="L51" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M51" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N51" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O51">
         <v>0</v>
@@ -8806,16 +8788,16 @@
         <v>539</v>
       </c>
       <c r="AD51" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="AE51" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="AF51" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="AP51" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="AQ51" t="s">
         <v>23</v>
@@ -8826,7 +8808,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="C52">
         <v>24</v>
@@ -8835,10 +8817,10 @@
         <v>195</v>
       </c>
       <c r="E52" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G52" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H52">
         <v>4</v>
@@ -8853,13 +8835,13 @@
         <v>702</v>
       </c>
       <c r="L52" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M52" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N52" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O52">
         <v>0</v>
@@ -8895,10 +8877,10 @@
         <v>608</v>
       </c>
       <c r="AF52" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="AP52" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="AQ52" t="s">
         <v>23</v>
@@ -8909,7 +8891,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="C53">
         <v>25</v>
@@ -8918,10 +8900,10 @@
         <v>195</v>
       </c>
       <c r="E53" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G53" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H53">
         <v>4</v>
@@ -8936,13 +8918,13 @@
         <v>702</v>
       </c>
       <c r="L53" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M53" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N53" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O53">
         <v>0</v>
@@ -8978,10 +8960,10 @@
         <v>612</v>
       </c>
       <c r="AF53" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="AP53" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="AQ53" t="s">
         <v>23</v>
@@ -8992,7 +8974,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -9001,10 +8983,10 @@
         <v>195</v>
       </c>
       <c r="E54" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G54" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H54">
         <v>4</v>
@@ -9019,13 +9001,13 @@
         <v>702</v>
       </c>
       <c r="L54" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M54" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N54" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O54">
         <v>0</v>
@@ -9058,13 +9040,13 @@
         <v>452</v>
       </c>
       <c r="AE54" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="AF54" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="AP54" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="AQ54" t="s">
         <v>23</v>
@@ -9075,7 +9057,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="C55">
         <v>26</v>
@@ -9084,10 +9066,10 @@
         <v>195</v>
       </c>
       <c r="E55" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G55" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H55">
         <v>4</v>
@@ -9102,13 +9084,13 @@
         <v>702</v>
       </c>
       <c r="L55" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M55" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="N55" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="O55">
         <v>0</v>
@@ -9144,10 +9126,10 @@
         <v>616</v>
       </c>
       <c r="AF55" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="AP55" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="AQ55" t="s">
         <v>23</v>
@@ -9158,7 +9140,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="C56">
         <v>27</v>
@@ -9167,10 +9149,10 @@
         <v>195</v>
       </c>
       <c r="E56" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G56" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H56">
         <v>4</v>
@@ -9185,13 +9167,13 @@
         <v>702</v>
       </c>
       <c r="L56" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M56" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N56" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O56">
         <v>0</v>
@@ -9227,10 +9209,10 @@
         <v>620</v>
       </c>
       <c r="AF56" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="AP56" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="AQ56" t="s">
         <v>23</v>
@@ -9241,7 +9223,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -9250,10 +9232,10 @@
         <v>51</v>
       </c>
       <c r="E57" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G57" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H57">
         <v>4</v>
@@ -9268,13 +9250,13 @@
         <v>702</v>
       </c>
       <c r="L57" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M57" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N57" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O57">
         <v>0</v>
@@ -9310,10 +9292,10 @@
         <v>452</v>
       </c>
       <c r="AF57" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="AP57" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="AQ57" t="s">
         <v>23</v>
@@ -9324,7 +9306,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="C58">
         <v>28</v>
@@ -9333,10 +9315,10 @@
         <v>86</v>
       </c>
       <c r="E58" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G58" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H58">
         <v>86</v>
@@ -9351,13 +9333,13 @@
         <v>702</v>
       </c>
       <c r="L58" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M58" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="N58" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="O58">
         <v>0</v>
@@ -9396,7 +9378,7 @@
         <v>623</v>
       </c>
       <c r="AP58" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="AQ58" t="s">
         <v>23</v>
@@ -9407,7 +9389,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="C59">
         <v>2</v>
@@ -9416,10 +9398,10 @@
         <v>36</v>
       </c>
       <c r="E59" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G59" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H59">
         <v>36</v>
@@ -9428,19 +9410,19 @@
         <v>2</v>
       </c>
       <c r="J59" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="K59" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="L59" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M59" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N59" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -9470,16 +9452,16 @@
         <v>539</v>
       </c>
       <c r="AD59" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="AE59" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="AF59" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="AP59" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="AQ59" t="s">
         <v>23</v>
@@ -9490,7 +9472,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -9499,10 +9481,10 @@
         <v>38</v>
       </c>
       <c r="E60" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G60" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H60">
         <v>38</v>
@@ -9511,19 +9493,19 @@
         <v>3</v>
       </c>
       <c r="J60" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="K60" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="L60" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M60" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N60" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -9553,16 +9535,16 @@
         <v>539</v>
       </c>
       <c r="AD60" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="AE60" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="AF60" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="AP60" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="AQ60" t="s">
         <v>23</v>
@@ -9573,7 +9555,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -9582,13 +9564,13 @@
         <v>196</v>
       </c>
       <c r="E61" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
       <c r="F61">
         <v>2</v>
       </c>
       <c r="G61" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H61">
         <v>196</v>
@@ -9603,13 +9585,13 @@
         <v>700</v>
       </c>
       <c r="L61" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M61" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N61" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -9639,16 +9621,16 @@
         <v>539</v>
       </c>
       <c r="AD61" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="AE61" t="s">
         <v>452</v>
       </c>
       <c r="AF61" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="AP61" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
       <c r="AQ61" t="s">
         <v>23</v>
@@ -9659,7 +9641,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
       <c r="C62">
         <v>26</v>
@@ -9668,10 +9650,10 @@
         <v>195</v>
       </c>
       <c r="E62" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G62" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H62">
         <v>195</v>
@@ -9686,13 +9668,13 @@
         <v>700</v>
       </c>
       <c r="L62" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M62" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="N62" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -9722,16 +9704,16 @@
         <v>614</v>
       </c>
       <c r="AD62" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="AE62" t="s">
         <v>452</v>
       </c>
       <c r="AF62" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="AP62" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="AQ62" t="s">
         <v>23</v>
@@ -9742,7 +9724,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="C63">
         <v>29</v>
@@ -9751,10 +9733,10 @@
         <v>14</v>
       </c>
       <c r="E63" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G63" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H63">
         <v>14</v>
@@ -9769,13 +9751,13 @@
         <v>700</v>
       </c>
       <c r="L63" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M63" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N63" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -9811,10 +9793,10 @@
         <v>627</v>
       </c>
       <c r="AF63" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="AP63" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="AQ63" t="s">
         <v>23</v>
@@ -9825,19 +9807,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="C64">
         <v>30</v>
       </c>
       <c r="E64" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="F64">
         <v>6</v>
       </c>
       <c r="G64" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H64">
         <v>195</v>
@@ -9852,13 +9834,13 @@
         <v>700</v>
       </c>
       <c r="L64" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M64" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N64" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -9894,10 +9876,10 @@
         <v>631</v>
       </c>
       <c r="AF64" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
       <c r="AP64" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="AQ64" t="s">
         <v>23</v>
@@ -9908,7 +9890,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="C65">
         <v>2</v>
@@ -9917,10 +9899,10 @@
         <v>195</v>
       </c>
       <c r="E65" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G65" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H65">
         <v>83</v>
@@ -9935,13 +9917,13 @@
         <v>700</v>
       </c>
       <c r="L65" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M65" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N65" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -9971,16 +9953,16 @@
         <v>539</v>
       </c>
       <c r="AD65" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="AE65" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="AF65" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="AP65" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="AQ65" t="s">
         <v>23</v>
@@ -9991,7 +9973,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="C66">
         <v>2</v>
@@ -10000,10 +9982,10 @@
         <v>195</v>
       </c>
       <c r="E66" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G66" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H66">
         <v>195</v>
@@ -10018,13 +10000,13 @@
         <v>700</v>
       </c>
       <c r="L66" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M66" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N66" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -10054,16 +10036,16 @@
         <v>539</v>
       </c>
       <c r="AD66" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="AE66" t="s">
         <v>452</v>
       </c>
       <c r="AF66" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="AP66" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="AQ66" t="s">
         <v>23</v>
@@ -10074,19 +10056,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>1053</v>
+        <v>1047</v>
       </c>
       <c r="C67">
         <v>31</v>
       </c>
       <c r="E67" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="F67">
         <v>7</v>
       </c>
       <c r="G67" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H67">
         <v>51</v>
@@ -10101,13 +10083,13 @@
         <v>700</v>
       </c>
       <c r="L67" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M67" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N67" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O67">
         <v>0</v>
@@ -10143,10 +10125,10 @@
         <v>635</v>
       </c>
       <c r="AF67" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="AP67" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="AQ67" t="s">
         <v>23</v>
@@ -10157,7 +10139,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="C68">
         <v>2</v>
@@ -10166,10 +10148,10 @@
         <v>195</v>
       </c>
       <c r="E68" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G68" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H68">
         <v>115</v>
@@ -10184,13 +10166,13 @@
         <v>700</v>
       </c>
       <c r="L68" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M68" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N68" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O68">
         <v>0</v>
@@ -10220,16 +10202,16 @@
         <v>539</v>
       </c>
       <c r="AD68" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="AE68" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="AF68" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="AP68" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="AQ68" t="s">
         <v>23</v>
@@ -10240,7 +10222,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>1061</v>
+        <v>1055</v>
       </c>
       <c r="C69">
         <v>2</v>
@@ -10249,10 +10231,10 @@
         <v>195</v>
       </c>
       <c r="E69" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G69" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H69">
         <v>195</v>
@@ -10267,13 +10249,13 @@
         <v>700</v>
       </c>
       <c r="L69" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M69" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="N69" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -10303,16 +10285,16 @@
         <v>539</v>
       </c>
       <c r="AD69" t="s">
-        <v>1062</v>
+        <v>1056</v>
       </c>
       <c r="AE69" t="s">
         <v>452</v>
       </c>
       <c r="AF69" t="s">
-        <v>1063</v>
+        <v>1057</v>
       </c>
       <c r="AP69" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
       <c r="AQ69" t="s">
         <v>23</v>
@@ -10323,7 +10305,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="C70">
         <v>26</v>
@@ -10332,13 +10314,13 @@
         <v>196</v>
       </c>
       <c r="E70" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
       <c r="F70">
         <v>2</v>
       </c>
       <c r="G70" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H70">
         <v>196</v>
@@ -10353,13 +10335,13 @@
         <v>700</v>
       </c>
       <c r="L70" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M70" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="N70" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="O70">
         <v>0</v>
@@ -10389,16 +10371,16 @@
         <v>614</v>
       </c>
       <c r="AD70" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
       <c r="AE70" t="s">
         <v>452</v>
       </c>
       <c r="AF70" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="AP70" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="AQ70" t="s">
         <v>23</v>
@@ -10409,7 +10391,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
       <c r="C71">
         <v>32</v>
@@ -10418,10 +10400,10 @@
         <v>195</v>
       </c>
       <c r="E71" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G71" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H71">
         <v>51</v>
@@ -10436,13 +10418,13 @@
         <v>700</v>
       </c>
       <c r="L71" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M71" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N71" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -10478,10 +10460,10 @@
         <v>452</v>
       </c>
       <c r="AF71" t="s">
-        <v>1070</v>
+        <v>1064</v>
       </c>
       <c r="AP71" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="AQ71" t="s">
         <v>23</v>
@@ -10492,7 +10474,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="C72">
         <v>33</v>
@@ -10501,10 +10483,10 @@
         <v>195</v>
       </c>
       <c r="E72" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G72" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H72">
         <v>117</v>
@@ -10519,13 +10501,13 @@
         <v>700</v>
       </c>
       <c r="L72" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M72" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N72" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -10564,7 +10546,7 @@
         <v>640</v>
       </c>
       <c r="AP72" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="AQ72" t="s">
         <v>23</v>
@@ -10575,19 +10557,19 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="C73">
         <v>34</v>
       </c>
       <c r="E73" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="F73">
         <v>2</v>
       </c>
       <c r="G73" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H73">
         <v>195</v>
@@ -10602,13 +10584,13 @@
         <v>700</v>
       </c>
       <c r="L73" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M73" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N73" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O73">
         <v>0</v>
@@ -10644,10 +10626,10 @@
         <v>644</v>
       </c>
       <c r="AF73" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="AP73" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="AQ73" t="s">
         <v>23</v>
@@ -10658,19 +10640,19 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="C74">
         <v>35</v>
       </c>
       <c r="E74" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="F74">
         <v>2</v>
       </c>
       <c r="G74" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H74">
         <v>51</v>
@@ -10685,13 +10667,13 @@
         <v>700</v>
       </c>
       <c r="L74" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M74" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N74" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O74">
         <v>0</v>
@@ -10727,10 +10709,10 @@
         <v>452</v>
       </c>
       <c r="AF74" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="AP74" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
       <c r="AQ74" t="s">
         <v>23</v>
@@ -10741,7 +10723,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="C75">
         <v>36</v>
@@ -10750,10 +10732,10 @@
         <v>20</v>
       </c>
       <c r="E75" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G75" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H75">
         <v>20</v>
@@ -10768,13 +10750,13 @@
         <v>700</v>
       </c>
       <c r="L75" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M75" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="N75" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="O75">
         <v>0</v>
@@ -10810,10 +10792,10 @@
         <v>452</v>
       </c>
       <c r="AF75" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="AP75" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="AQ75" t="s">
         <v>23</v>
@@ -10824,7 +10806,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="C76">
         <v>2</v>
@@ -10833,10 +10815,10 @@
         <v>195</v>
       </c>
       <c r="E76" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G76" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H76">
         <v>195</v>
@@ -10851,13 +10833,13 @@
         <v>700</v>
       </c>
       <c r="L76" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M76" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N76" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O76">
         <v>0</v>
@@ -10887,16 +10869,16 @@
         <v>539</v>
       </c>
       <c r="AD76" t="s">
-        <v>1084</v>
+        <v>1078</v>
       </c>
       <c r="AE76" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="AF76" t="s">
-        <v>1086</v>
+        <v>1080</v>
       </c>
       <c r="AP76" t="s">
-        <v>1087</v>
+        <v>1081</v>
       </c>
       <c r="AQ76" t="s">
         <v>23</v>
@@ -10907,19 +10889,19 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="C77">
         <v>37</v>
       </c>
       <c r="E77" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="G77" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="I77">
         <v>3</v>
@@ -10931,13 +10913,13 @@
         <v>700</v>
       </c>
       <c r="L77" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M77" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N77" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O77">
         <v>0</v>
@@ -10973,10 +10955,10 @@
         <v>452</v>
       </c>
       <c r="AF77" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="AP77" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="AQ77" t="s">
         <v>23</v>
@@ -10987,7 +10969,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="C78">
         <v>38</v>
@@ -10996,10 +10978,10 @@
         <v>51</v>
       </c>
       <c r="E78" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G78" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H78">
         <v>51</v>
@@ -11014,13 +10996,13 @@
         <v>700</v>
       </c>
       <c r="L78" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M78" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N78" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O78">
         <v>0</v>
@@ -11059,7 +11041,7 @@
         <v>653</v>
       </c>
       <c r="AP78" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="AQ78" t="s">
         <v>23</v>
@@ -11070,7 +11052,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="C79">
         <v>28</v>
@@ -11079,10 +11061,10 @@
         <v>86</v>
       </c>
       <c r="E79" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G79" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H79">
         <v>86</v>
@@ -11097,13 +11079,13 @@
         <v>700</v>
       </c>
       <c r="L79" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M79" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="N79" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -11136,13 +11118,13 @@
         <v>452</v>
       </c>
       <c r="AE79" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="AF79" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="AP79" t="s">
-        <v>1095</v>
+        <v>1089</v>
       </c>
       <c r="AQ79" t="s">
         <v>23</v>
@@ -11153,7 +11135,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>1096</v>
+        <v>1090</v>
       </c>
       <c r="C80">
         <v>39</v>
@@ -11162,10 +11144,10 @@
         <v>95</v>
       </c>
       <c r="E80" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G80" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H80">
         <v>95</v>
@@ -11180,13 +11162,13 @@
         <v>700</v>
       </c>
       <c r="L80" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M80" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N80" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O80">
         <v>0</v>
@@ -11222,10 +11204,10 @@
         <v>452</v>
       </c>
       <c r="AF80" t="s">
-        <v>1097</v>
+        <v>1091</v>
       </c>
       <c r="AP80" t="s">
-        <v>1098</v>
+        <v>1092</v>
       </c>
       <c r="AQ80" t="s">
         <v>23</v>
@@ -11236,7 +11218,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="C81">
         <v>40</v>
@@ -11245,10 +11227,10 @@
         <v>69</v>
       </c>
       <c r="E81" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G81" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H81">
         <v>69</v>
@@ -11263,13 +11245,13 @@
         <v>700</v>
       </c>
       <c r="L81" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="M81" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N81" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O81">
         <v>0</v>
@@ -11308,7 +11290,7 @@
         <v>658</v>
       </c>
       <c r="AP81" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="AQ81" t="s">
         <v>23</v>
@@ -11319,34 +11301,34 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="C82">
         <v>41</v>
       </c>
       <c r="E82" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G82" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="I82">
         <v>1</v>
       </c>
       <c r="J82" t="s">
-        <v>1102</v>
+        <v>1096</v>
       </c>
       <c r="K82" t="s">
-        <v>1102</v>
+        <v>1096</v>
       </c>
       <c r="L82" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="M82" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="N82" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="O82">
         <v>0</v>
@@ -11382,10 +11364,10 @@
         <v>452</v>
       </c>
       <c r="AF82" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
       <c r="AP82" t="s">
-        <v>1104</v>
+        <v>1098</v>
       </c>
       <c r="AQ82" t="s">
         <v>23</v>
@@ -11407,7 +11389,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>695</v>
@@ -11419,10 +11401,10 @@
         <v>709</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1107</v>
+        <v>1101</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>713</v>
@@ -13422,16 +13404,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>713</v>
@@ -13456,31 +13438,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1111</v>
+        <v>1105</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>694</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1114</v>
+        <v>1108</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1115</v>
+        <v>1109</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>713</v>
@@ -13502,40 +13484,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>1116</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>1117</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>1118</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>1119</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>1120</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>791</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>1121</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>1122</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>1123</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>1124</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>713</v>
@@ -13560,28 +13542,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1126</v>
+        <v>1120</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1127</v>
+        <v>1121</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1128</v>
+        <v>1122</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>713</v>
@@ -13595,10 +13577,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="C2" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D2">
         <v>3</v>
@@ -13610,7 +13592,7 @@
         <v>980000</v>
       </c>
       <c r="G2" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="H2">
         <v>195</v>
@@ -13619,7 +13601,7 @@
         <v>704</v>
       </c>
       <c r="J2" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
       <c r="K2" t="s">
         <v>723</v>
@@ -13630,10 +13612,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
       <c r="C3" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D3">
         <v>9</v>
@@ -13645,16 +13627,16 @@
         <v>490000</v>
       </c>
       <c r="G3" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="H3">
         <v>195</v>
       </c>
       <c r="I3" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="J3" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
       <c r="K3" t="s">
         <v>728</v>
@@ -13665,10 +13647,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1134</v>
+        <v>1128</v>
       </c>
       <c r="C4" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D4">
         <v>11</v>
@@ -13680,16 +13662,16 @@
         <v>255000</v>
       </c>
       <c r="G4" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="H4">
         <v>51</v>
       </c>
       <c r="I4" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="J4" t="s">
-        <v>1135</v>
+        <v>1129</v>
       </c>
       <c r="K4" t="s">
         <v>728</v>
@@ -13700,10 +13682,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1136</v>
+        <v>1130</v>
       </c>
       <c r="C5" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D5">
         <v>19</v>
@@ -13715,7 +13697,7 @@
         <v>490000</v>
       </c>
       <c r="G5" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="H5">
         <v>196</v>
@@ -13724,7 +13706,7 @@
         <v>701</v>
       </c>
       <c r="J5" t="s">
-        <v>1137</v>
+        <v>1131</v>
       </c>
       <c r="K5" t="s">
         <v>732</v>
@@ -13735,10 +13717,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1138</v>
+        <v>1132</v>
       </c>
       <c r="C6" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D6">
         <v>25</v>
@@ -13750,7 +13732,7 @@
         <v>260000</v>
       </c>
       <c r="G6" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="H6">
         <v>195</v>
@@ -13759,7 +13741,7 @@
         <v>701</v>
       </c>
       <c r="J6" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="K6" t="s">
         <v>732</v>
@@ -13770,10 +13752,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>1140</v>
+        <v>1134</v>
       </c>
       <c r="C7" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D7">
         <v>28</v>
@@ -13785,7 +13767,7 @@
         <v>52000</v>
       </c>
       <c r="G7" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="H7">
         <v>38</v>
@@ -13794,7 +13776,7 @@
         <v>701</v>
       </c>
       <c r="J7" t="s">
-        <v>1141</v>
+        <v>1135</v>
       </c>
       <c r="K7" t="s">
         <v>732</v>
@@ -13805,10 +13787,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1142</v>
+        <v>1136</v>
       </c>
       <c r="C8" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D8">
         <v>29</v>
@@ -13820,7 +13802,7 @@
         <v>510000</v>
       </c>
       <c r="G8" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="H8">
         <v>51</v>
@@ -13829,7 +13811,7 @@
         <v>701</v>
       </c>
       <c r="J8" t="s">
-        <v>1143</v>
+        <v>1137</v>
       </c>
       <c r="K8" t="s">
         <v>732</v>
@@ -13840,10 +13822,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1144</v>
+        <v>1138</v>
       </c>
       <c r="C9" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D9">
         <v>30</v>
@@ -13855,16 +13837,16 @@
         <v>1150000</v>
       </c>
       <c r="G9" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="H9">
         <v>4</v>
       </c>
       <c r="I9" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="J9" t="s">
-        <v>1145</v>
+        <v>1139</v>
       </c>
       <c r="K9" t="s">
         <v>736</v>
@@ -13875,10 +13857,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1146</v>
+        <v>1140</v>
       </c>
       <c r="C10" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D10">
         <v>40</v>
@@ -13890,16 +13872,16 @@
         <v>980000</v>
       </c>
       <c r="G10" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="H10">
         <v>4</v>
       </c>
       <c r="I10" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="J10" t="s">
-        <v>1147</v>
+        <v>1141</v>
       </c>
       <c r="K10" t="s">
         <v>736</v>
@@ -13910,10 +13892,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>1148</v>
+        <v>1142</v>
       </c>
       <c r="C11" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D11">
         <v>43</v>
@@ -13925,16 +13907,16 @@
         <v>52000</v>
       </c>
       <c r="G11" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="H11">
         <v>14</v>
       </c>
       <c r="I11" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="J11" t="s">
-        <v>1149</v>
+        <v>1143</v>
       </c>
       <c r="K11" t="s">
         <v>736</v>
@@ -13945,10 +13927,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>1150</v>
+        <v>1144</v>
       </c>
       <c r="C12" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D12">
         <v>49</v>
@@ -13960,7 +13942,7 @@
         <v>170000</v>
       </c>
       <c r="G12" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="H12">
         <v>14</v>
@@ -13969,7 +13951,7 @@
         <v>702</v>
       </c>
       <c r="J12" t="s">
-        <v>1151</v>
+        <v>1145</v>
       </c>
       <c r="K12" t="s">
         <v>740</v>
@@ -13980,10 +13962,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>1152</v>
+        <v>1146</v>
       </c>
       <c r="C13" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D13">
         <v>54</v>
@@ -13995,7 +13977,7 @@
         <v>144000</v>
       </c>
       <c r="G13" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="H13">
         <v>4</v>
@@ -14004,7 +13986,7 @@
         <v>702</v>
       </c>
       <c r="J13" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="K13" t="s">
         <v>740</v>
@@ -14015,10 +13997,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="C14" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D14">
         <v>57</v>
@@ -14030,7 +14012,7 @@
         <v>490000</v>
       </c>
       <c r="G14" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="H14">
         <v>86</v>
@@ -14039,7 +14021,7 @@
         <v>702</v>
       </c>
       <c r="J14" t="s">
-        <v>1155</v>
+        <v>1149</v>
       </c>
       <c r="K14" t="s">
         <v>740</v>
@@ -14050,10 +14032,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>1156</v>
+        <v>1150</v>
       </c>
       <c r="C15" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D15">
         <v>61</v>
@@ -14065,7 +14047,7 @@
         <v>48000</v>
       </c>
       <c r="G15" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="H15">
         <v>195</v>
@@ -14074,7 +14056,7 @@
         <v>700</v>
       </c>
       <c r="J15" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="K15" t="s">
         <v>743</v>
@@ -14085,10 +14067,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>1158</v>
+        <v>1152</v>
       </c>
       <c r="C16" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D16">
         <v>68</v>
@@ -14100,7 +14082,7 @@
         <v>980000</v>
       </c>
       <c r="G16" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="H16">
         <v>195</v>
@@ -14109,7 +14091,7 @@
         <v>700</v>
       </c>
       <c r="J16" t="s">
-        <v>1159</v>
+        <v>1153</v>
       </c>
       <c r="K16" t="s">
         <v>743</v>
@@ -14120,10 +14102,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>1160</v>
+        <v>1154</v>
       </c>
       <c r="C17" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D17">
         <v>69</v>
@@ -14135,7 +14117,7 @@
         <v>980000</v>
       </c>
       <c r="G17" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="H17">
         <v>196</v>
@@ -14144,7 +14126,7 @@
         <v>700</v>
       </c>
       <c r="J17" t="s">
-        <v>1161</v>
+        <v>1155</v>
       </c>
       <c r="K17" t="s">
         <v>743</v>
@@ -14155,10 +14137,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
       <c r="C18" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D18">
         <v>74</v>
@@ -14170,7 +14152,7 @@
         <v>294000</v>
       </c>
       <c r="G18" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="H18">
         <v>20</v>
@@ -14179,7 +14161,7 @@
         <v>700</v>
       </c>
       <c r="J18" t="s">
-        <v>1163</v>
+        <v>1157</v>
       </c>
       <c r="K18" t="s">
         <v>743</v>
@@ -14190,10 +14172,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>1164</v>
+        <v>1158</v>
       </c>
       <c r="C19" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D19">
         <v>78</v>
@@ -14205,7 +14187,7 @@
         <v>294000</v>
       </c>
       <c r="G19" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="H19">
         <v>86</v>
@@ -14214,7 +14196,7 @@
         <v>700</v>
       </c>
       <c r="J19" t="s">
-        <v>1165</v>
+        <v>1159</v>
       </c>
       <c r="K19" t="s">
         <v>743</v>
@@ -14236,28 +14218,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1167</v>
+        <v>1161</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1127</v>
+        <v>1121</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1168</v>
+        <v>1162</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1169</v>
+        <v>1163</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1170</v>
+        <v>1164</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>713</v>
@@ -14288,13 +14270,13 @@
         <v>477</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1172</v>
+        <v>1166</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>19</v>
@@ -14328,7 +14310,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1173</v>
+        <v>1167</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>19</v>
@@ -14345,10 +14327,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1174</v>
+        <v>1168</v>
       </c>
       <c r="C2" t="s">
-        <v>1175</v>
+        <v>1169</v>
       </c>
       <c r="D2">
         <v>5000</v>
@@ -14357,7 +14339,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
     </row>
   </sheetData>
@@ -14388,19 +14370,19 @@
         <v>477</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1177</v>
+        <v>1171</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1178</v>
+        <v>1172</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1179</v>
+        <v>1173</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1180</v>
+        <v>1174</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>19</v>
@@ -18590,28 +18572,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1182</v>
+        <v>1176</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1183</v>
+        <v>1177</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1184</v>
+        <v>1178</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>526</v>
@@ -18626,22 +18608,22 @@
         <v>529</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>1189</v>
+        <v>1183</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>713</v>
@@ -18666,28 +18648,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1126</v>
+        <v>1120</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1127</v>
+        <v>1121</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>713</v>
@@ -18718,16 +18700,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1190</v>
+        <v>1184</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1191</v>
+        <v>1185</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>662</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1192</v>
+        <v>1186</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>19</v>
@@ -18741,13 +18723,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="C2" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="E2" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -18756,7 +18738,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
     </row>
   </sheetData>
@@ -18795,16 +18777,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1197</v>
+        <v>1191</v>
       </c>
       <c r="C2" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -18812,16 +18794,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="C3" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -18829,16 +18811,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="C4" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -18846,7 +18828,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
       <c r="C5" t="s">
         <v>154</v>
@@ -18855,7 +18837,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -18863,7 +18845,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1204</v>
+        <v>1198</v>
       </c>
       <c r="C6" t="s">
         <v>157</v>
@@ -18872,7 +18854,7 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -18880,7 +18862,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="C7" t="s">
         <v>355</v>
@@ -18889,7 +18871,7 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -18897,7 +18879,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="C8" t="s">
         <v>358</v>
@@ -18906,7 +18888,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -18914,16 +18896,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="C9" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -18931,16 +18913,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="C10" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -18948,16 +18930,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="C11" t="s">
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -18965,16 +18947,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>1213</v>
+        <v>1207</v>
       </c>
       <c r="C12" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
     </row>
   </sheetData>
@@ -19013,10 +18995,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1215</v>
+        <v>1209</v>
       </c>
       <c r="C2" t="s">
-        <v>1216</v>
+        <v>1210</v>
       </c>
       <c r="D2" t="s">
         <v>452</v>
@@ -19025,7 +19007,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -19033,10 +19015,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1217</v>
+        <v>1211</v>
       </c>
       <c r="C3" t="s">
-        <v>1218</v>
+        <v>1212</v>
       </c>
       <c r="D3" t="s">
         <v>452</v>
@@ -19045,7 +19027,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -19053,10 +19035,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
       <c r="C4" t="s">
-        <v>1220</v>
+        <v>1214</v>
       </c>
       <c r="D4" t="s">
         <v>452</v>
@@ -19065,7 +19047,7 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -19073,10 +19055,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1221</v>
+        <v>1215</v>
       </c>
       <c r="C5" t="s">
-        <v>1222</v>
+        <v>1216</v>
       </c>
       <c r="D5" t="s">
         <v>452</v>
@@ -19085,7 +19067,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -19093,13 +19075,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1223</v>
+        <v>1217</v>
       </c>
       <c r="C6" t="s">
-        <v>1224</v>
+        <v>1218</v>
       </c>
       <c r="D6" t="s">
-        <v>1225</v>
+        <v>1219</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -19153,28 +19135,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1226</v>
+        <v>1220</v>
       </c>
       <c r="C2" t="s">
-        <v>1227</v>
+        <v>1221</v>
       </c>
       <c r="D2" t="s">
-        <v>1228</v>
+        <v>1222</v>
       </c>
       <c r="E2" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="F2" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="I2" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -19182,28 +19164,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1232</v>
+        <v>1226</v>
       </c>
       <c r="C3" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="D3" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="E3" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="F3" t="s">
-        <v>1236</v>
+        <v>1230</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="I3" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -19211,16 +19193,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1237</v>
+        <v>1231</v>
       </c>
       <c r="C4" t="s">
-        <v>1238</v>
+        <v>1232</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>1239</v>
+        <v>1233</v>
       </c>
       <c r="I4" t="s">
         <v>23</v>
@@ -19231,16 +19213,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1240</v>
+        <v>1234</v>
       </c>
       <c r="C5" t="s">
-        <v>1241</v>
+        <v>1235</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>1239</v>
+        <v>1233</v>
       </c>
       <c r="I5" t="s">
         <v>23</v>
@@ -19251,16 +19233,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
       <c r="C6" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>1239</v>
+        <v>1233</v>
       </c>
       <c r="I6" t="s">
         <v>23</v>
@@ -19271,16 +19253,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>1244</v>
+        <v>1238</v>
       </c>
       <c r="C7" t="s">
-        <v>1245</v>
+        <v>1239</v>
       </c>
       <c r="G7">
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>1239</v>
+        <v>1233</v>
       </c>
       <c r="I7" t="s">
         <v>23</v>
@@ -19291,16 +19273,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1246</v>
+        <v>1240</v>
       </c>
       <c r="C8" t="s">
-        <v>1247</v>
+        <v>1241</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>1239</v>
+        <v>1233</v>
       </c>
       <c r="I8" t="s">
         <v>23</v>
@@ -19322,19 +19304,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1248</v>
+        <v>1242</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1249</v>
+        <v>1243</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1250</v>
+        <v>1244</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>713</v>
@@ -19362,10 +19344,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1252</v>
+        <v>1246</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>694</v>
@@ -19374,37 +19356,37 @@
         <v>707</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>708</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1254</v>
+        <v>1248</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1255</v>
+        <v>1249</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>1256</v>
+        <v>1250</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>713</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>1257</v>
+        <v>1251</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>5</v>
@@ -19432,7 +19414,7 @@
         <v>695</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1259</v>
+        <v>1253</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>696</v>
@@ -19441,7 +19423,7 @@
         <v>709</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>713</v>
@@ -19463,16 +19445,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1261</v>
+        <v>1255</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1264</v>
+        <v>1258</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -19567,13 +19549,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1265</v>
+        <v>1259</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1266</v>
+        <v>1260</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1267</v>
+        <v>1261</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>713</v>
@@ -19587,22 +19569,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1268</v>
+        <v>1262</v>
       </c>
       <c r="C2" t="s">
-        <v>1269</v>
+        <v>1263</v>
       </c>
       <c r="D2">
         <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>1270</v>
+        <v>1264</v>
       </c>
       <c r="G2" t="s">
-        <v>1271</v>
+        <v>1265</v>
       </c>
       <c r="H2" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
     </row>
   </sheetData>
@@ -19624,13 +19606,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>695</v>
@@ -19639,7 +19621,7 @@
         <v>696</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1127</v>
+        <v>1121</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>713</v>
@@ -19661,10 +19643,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1273</v>
+        <v>1267</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1274</v>
+        <v>1268</v>
       </c>
     </row>
   </sheetData>
@@ -19683,37 +19665,37 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>1275</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>1276</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>1277</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>1278</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>1279</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>1280</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>1281</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>1282</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>1283</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>1284</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>1285</v>
       </c>
     </row>
   </sheetData>
@@ -19732,13 +19714,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1286</v>
+        <v>1280</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1287</v>
+        <v>1281</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>694</v>
@@ -19747,10 +19729,10 @@
         <v>711</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1288</v>
+        <v>1282</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1127</v>
+        <v>1121</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>713</v>
@@ -19775,7 +19757,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1289</v>
+        <v>1283</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>695</v>
@@ -19800,40 +19782,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1290</v>
+        <v>1284</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>711</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>1291</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>1292</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>1293</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>1294</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>1295</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>1296</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>1297</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>1298</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>1299</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>713</v>
@@ -19878,7 +19860,7 @@
         <v>50000</v>
       </c>
       <c r="D2" t="s">
-        <v>1300</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -19892,7 +19874,7 @@
         <v>50000</v>
       </c>
       <c r="D3" t="s">
-        <v>1301</v>
+        <v>1295</v>
       </c>
     </row>
   </sheetData>
@@ -19942,10 +19924,10 @@
         <v>696</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>711</v>
@@ -20515,7 +20497,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>481</v>
@@ -20524,7 +20506,7 @@
         <v>696</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>713</v>
@@ -20546,57 +20528,57 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1302</v>
+        <v>1296</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1305</v>
+        <v>1299</v>
       </c>
       <c r="B2" t="s">
         <v>701</v>
       </c>
       <c r="C2" t="s">
-        <v>1306</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1307</v>
+        <v>1301</v>
       </c>
       <c r="B3" t="s">
-        <v>1308</v>
+        <v>1302</v>
       </c>
       <c r="C3" t="s">
-        <v>1306</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1309</v>
+        <v>1303</v>
       </c>
       <c r="B4" t="s">
-        <v>1310</v>
+        <v>1304</v>
       </c>
       <c r="C4" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1311</v>
+        <v>1305</v>
       </c>
       <c r="B5" t="s">
-        <v>1310</v>
+        <v>1304</v>
       </c>
       <c r="C5" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
     </row>
   </sheetData>
@@ -20617,18 +20599,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1312</v>
+        <v>1306</v>
       </c>
       <c r="B1" t="s">
-        <v>1313</v>
+        <v>1307</v>
       </c>
       <c r="C1" t="s">
-        <v>1314</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1315</v>
+        <v>1309</v>
       </c>
       <c r="B2" t="s">
         <v>452</v>
@@ -20639,10 +20621,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1316</v>
+        <v>1310</v>
       </c>
       <c r="B3" t="s">
-        <v>1317</v>
+        <v>1311</v>
       </c>
       <c r="C3" t="s">
         <v>452</v>
@@ -20650,10 +20632,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1318</v>
+        <v>1312</v>
       </c>
       <c r="B4" t="s">
-        <v>1319</v>
+        <v>1313</v>
       </c>
       <c r="C4" t="s">
         <v>452</v>
@@ -20661,10 +20643,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1320</v>
+        <v>1314</v>
       </c>
       <c r="B5" t="s">
-        <v>1321</v>
+        <v>1315</v>
       </c>
       <c r="C5" t="s">
         <v>452</v>
@@ -20672,10 +20654,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1322</v>
+        <v>1316</v>
       </c>
       <c r="B6" t="s">
-        <v>1323</v>
+        <v>1317</v>
       </c>
       <c r="C6" t="s">
         <v>452</v>
@@ -20683,10 +20665,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1324</v>
+        <v>1318</v>
       </c>
       <c r="B7" t="s">
-        <v>1325</v>
+        <v>1319</v>
       </c>
       <c r="C7" t="s">
         <v>452</v>
@@ -20694,10 +20676,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1326</v>
+        <v>1320</v>
       </c>
       <c r="B8" t="s">
-        <v>1327</v>
+        <v>1321</v>
       </c>
       <c r="C8" t="s">
         <v>452</v>
@@ -20705,10 +20687,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1328</v>
+        <v>1322</v>
       </c>
       <c r="B9" t="s">
-        <v>1329</v>
+        <v>1323</v>
       </c>
       <c r="C9" t="s">
         <v>452</v>
@@ -20716,10 +20698,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="B10" t="s">
-        <v>1331</v>
+        <v>1325</v>
       </c>
       <c r="C10" t="s">
         <v>452</v>
@@ -20727,10 +20709,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1332</v>
+        <v>1326</v>
       </c>
       <c r="B11" t="s">
-        <v>1333</v>
+        <v>1327</v>
       </c>
       <c r="C11" t="s">
         <v>452</v>
@@ -20738,10 +20720,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1334</v>
+        <v>1328</v>
       </c>
       <c r="B12" t="s">
-        <v>1323</v>
+        <v>1317</v>
       </c>
       <c r="C12" t="s">
         <v>452</v>
@@ -20760,7 +20742,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1335</v>
+        <v>1329</v>
       </c>
       <c r="B14" t="s">
         <v>452</v>
@@ -20774,7 +20756,7 @@
         <v>452</v>
       </c>
       <c r="B15" t="s">
-        <v>1336</v>
+        <v>1330</v>
       </c>
       <c r="C15" t="s">
         <v>452</v>
@@ -20785,7 +20767,7 @@
         <v>452</v>
       </c>
       <c r="B16" t="s">
-        <v>1337</v>
+        <v>1331</v>
       </c>
       <c r="C16" t="s">
         <v>452</v>
@@ -20796,7 +20778,7 @@
         <v>452</v>
       </c>
       <c r="B17" t="s">
-        <v>1338</v>
+        <v>1332</v>
       </c>
       <c r="C17" t="s">
         <v>452</v>
@@ -20807,7 +20789,7 @@
         <v>452</v>
       </c>
       <c r="B18" t="s">
-        <v>1339</v>
+        <v>1333</v>
       </c>
       <c r="C18" t="s">
         <v>452</v>
@@ -20818,7 +20800,7 @@
         <v>452</v>
       </c>
       <c r="B19" t="s">
-        <v>1340</v>
+        <v>1334</v>
       </c>
       <c r="C19" t="s">
         <v>452</v>
@@ -20829,7 +20811,7 @@
         <v>452</v>
       </c>
       <c r="B20" t="s">
-        <v>1341</v>
+        <v>1335</v>
       </c>
       <c r="C20" t="s">
         <v>452</v>
@@ -20840,7 +20822,7 @@
         <v>452</v>
       </c>
       <c r="B21" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="C21" t="s">
         <v>452</v>
@@ -20851,7 +20833,7 @@
         <v>452</v>
       </c>
       <c r="B22" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="C22" t="s">
         <v>452</v>
@@ -20862,7 +20844,7 @@
         <v>452</v>
       </c>
       <c r="B23" t="s">
-        <v>1344</v>
+        <v>1338</v>
       </c>
       <c r="C23" t="s">
         <v>452</v>
@@ -20873,7 +20855,7 @@
         <v>452</v>
       </c>
       <c r="B24" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="C24" t="s">
         <v>452</v>
@@ -20884,7 +20866,7 @@
         <v>452</v>
       </c>
       <c r="B25" t="s">
-        <v>1346</v>
+        <v>1340</v>
       </c>
       <c r="C25" t="s">
         <v>452</v>
@@ -20903,7 +20885,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
       <c r="B27" t="s">
         <v>452</v>
@@ -20917,10 +20899,10 @@
         <v>452</v>
       </c>
       <c r="B28" t="s">
-        <v>1348</v>
+        <v>1342</v>
       </c>
       <c r="C28" t="s">
-        <v>1349</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -20936,7 +20918,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1350</v>
+        <v>1344</v>
       </c>
       <c r="B30" t="s">
         <v>452</v>
@@ -20950,7 +20932,7 @@
         <v>452</v>
       </c>
       <c r="B31" t="s">
-        <v>1351</v>
+        <v>1345</v>
       </c>
       <c r="C31" t="s">
         <v>452</v>
@@ -20961,7 +20943,7 @@
         <v>452</v>
       </c>
       <c r="B32" t="s">
-        <v>1352</v>
+        <v>1346</v>
       </c>
       <c r="C32" t="s">
         <v>452</v>
@@ -20972,7 +20954,7 @@
         <v>452</v>
       </c>
       <c r="B33" t="s">
-        <v>1353</v>
+        <v>1347</v>
       </c>
       <c r="C33" t="s">
         <v>452</v>
@@ -20991,7 +20973,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1354</v>
+        <v>1348</v>
       </c>
       <c r="B35" t="s">
         <v>452</v>
@@ -21005,7 +20987,7 @@
         <v>452</v>
       </c>
       <c r="B36" t="s">
-        <v>1355</v>
+        <v>1349</v>
       </c>
       <c r="C36" t="s">
         <v>452</v>
@@ -21016,7 +20998,7 @@
         <v>452</v>
       </c>
       <c r="B37" t="s">
-        <v>1356</v>
+        <v>1350</v>
       </c>
       <c r="C37" t="s">
         <v>452</v>
@@ -21027,7 +21009,7 @@
         <v>452</v>
       </c>
       <c r="B38" t="s">
-        <v>1357</v>
+        <v>1351</v>
       </c>
       <c r="C38" t="s">
         <v>452</v>
@@ -21046,7 +21028,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1358</v>
+        <v>1352</v>
       </c>
       <c r="B40" t="s">
         <v>452</v>
@@ -23111,7 +23093,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>-24</v>
+        <v>9</v>
       </c>
       <c r="E10">
         <v>20</v>
@@ -23134,7 +23116,7 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>-16</v>
+        <v>17</v>
       </c>
       <c r="E11">
         <v>20</v>
@@ -23223,7 +23205,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -25220,31 +25202,28 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>714</v>
-      </c>
-      <c r="D67">
+        <v>724</v>
+      </c>
+      <c r="C67">
         <v>3</v>
-      </c>
-      <c r="E67">
-        <v>5</v>
       </c>
       <c r="F67">
         <v>7</v>
       </c>
       <c r="G67">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="H67">
         <v>0</v>
       </c>
       <c r="I67" t="s">
+        <v>734</v>
+      </c>
+      <c r="L67" t="s">
         <v>757</v>
       </c>
-      <c r="L67" t="s">
-        <v>758</v>
-      </c>
       <c r="M67" t="s">
-        <v>759</v>
+        <v>736</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
@@ -25261,19 +25240,19 @@
         <v>7</v>
       </c>
       <c r="G68">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="H68">
         <v>0</v>
       </c>
       <c r="I68" t="s">
-        <v>757</v>
+        <v>738</v>
       </c>
       <c r="L68" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="M68" t="s">
-        <v>759</v>
+        <v>740</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
@@ -25281,28 +25260,31 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>724</v>
-      </c>
-      <c r="C69">
+        <v>714</v>
+      </c>
+      <c r="D69">
         <v>3</v>
       </c>
+      <c r="E69">
+        <v>5</v>
+      </c>
       <c r="F69">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G69">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H69">
         <v>0</v>
       </c>
       <c r="I69" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="L69" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="M69" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
@@ -25316,22 +25298,22 @@
         <v>3</v>
       </c>
       <c r="F70">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G70">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H70">
         <v>0</v>
       </c>
       <c r="I70" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="L70" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="M70" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
@@ -25339,19 +25321,16 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>714</v>
-      </c>
-      <c r="D71">
+        <v>724</v>
+      </c>
+      <c r="C71">
         <v>3</v>
       </c>
-      <c r="E71">
-        <v>5</v>
-      </c>
       <c r="F71">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G71">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -25360,7 +25339,7 @@
         <v>741</v>
       </c>
       <c r="L71" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="M71" t="s">
         <v>743</v>
@@ -25374,143 +25353,24 @@
         <v>724</v>
       </c>
       <c r="C72">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F72">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G72">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H72">
         <v>0</v>
       </c>
       <c r="I72" t="s">
-        <v>741</v>
+        <v>721</v>
       </c>
       <c r="L72" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="M72" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73" t="s">
-        <v>724</v>
-      </c>
-      <c r="C73">
-        <v>3</v>
-      </c>
-      <c r="F73">
-        <v>7</v>
-      </c>
-      <c r="G73">
-        <v>7</v>
-      </c>
-      <c r="H73">
-        <v>0</v>
-      </c>
-      <c r="I73" t="s">
-        <v>741</v>
-      </c>
-      <c r="L73" t="s">
-        <v>764</v>
-      </c>
-      <c r="M73" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74" t="s">
-        <v>714</v>
-      </c>
-      <c r="D74">
-        <v>5</v>
-      </c>
-      <c r="E74">
-        <v>5</v>
-      </c>
-      <c r="F74">
-        <v>7</v>
-      </c>
-      <c r="G74">
-        <v>40</v>
-      </c>
-      <c r="H74">
-        <v>0</v>
-      </c>
-      <c r="I74" t="s">
-        <v>757</v>
-      </c>
-      <c r="L74" t="s">
-        <v>765</v>
-      </c>
-      <c r="M74" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>74</v>
-      </c>
-      <c r="B75" t="s">
-        <v>724</v>
-      </c>
-      <c r="C75">
-        <v>5</v>
-      </c>
-      <c r="F75">
-        <v>7</v>
-      </c>
-      <c r="G75">
-        <v>73</v>
-      </c>
-      <c r="H75">
-        <v>0</v>
-      </c>
-      <c r="I75" t="s">
-        <v>757</v>
-      </c>
-      <c r="L75" t="s">
-        <v>766</v>
-      </c>
-      <c r="M75" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>75</v>
-      </c>
-      <c r="B76" t="s">
-        <v>724</v>
-      </c>
-      <c r="C76">
-        <v>5</v>
-      </c>
-      <c r="F76">
-        <v>5</v>
-      </c>
-      <c r="G76">
-        <v>11</v>
-      </c>
-      <c r="H76">
-        <v>0</v>
-      </c>
-      <c r="I76" t="s">
-        <v>721</v>
-      </c>
-      <c r="L76" t="s">
-        <v>767</v>
-      </c>
-      <c r="M76" t="s">
         <v>723</v>
       </c>
     </row>
